--- a/database/event/4686/event_4686_evp_summary.xlsx
+++ b/database/event/4686/event_4686_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.7242</v>
+        <v>7.1303</v>
       </c>
       <c r="C2" t="n">
-        <v>1.1397</v>
+        <v>1.2085</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2951</v>
+        <v>2.3968</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7242</v>
+        <v>7.1303</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3755</v>
+        <v>3.7816</v>
       </c>
       <c r="G2" t="n">
         <v>3.3487</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3755</v>
+        <v>3.7816</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3755</v>
+        <v>3.7816</v>
       </c>
       <c r="J2" t="n">
         <v>3.3487</v>
@@ -529,7 +529,7 @@
         <v>79</v>
       </c>
       <c r="M2" t="n">
-        <v>6.7242</v>
+        <v>7.1303</v>
       </c>
       <c r="N2" t="n">
         <v>219</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.8489</v>
+        <v>3.6</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4829</v>
+        <v>0.6102</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7295</v>
+        <v>0.9903</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8489</v>
+        <v>3.6</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7663</v>
+        <v>2.5174</v>
       </c>
       <c r="G3" t="n">
         <v>1.0826</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7663</v>
+        <v>2.5174</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7663</v>
+        <v>2.5174</v>
       </c>
       <c r="J3" t="n">
         <v>1.0826</v>
@@ -575,7 +575,7 @@
         <v>79</v>
       </c>
       <c r="M3" t="n">
-        <v>2.8489</v>
+        <v>3.6</v>
       </c>
       <c r="N3" t="n">
         <v>207</v>
@@ -584,311 +584,311 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>buster</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.1475</v>
+        <v>3.0498</v>
       </c>
       <c r="C4" t="n">
-        <v>0.364</v>
+        <v>0.5169</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4462</v>
+        <v>0.7711</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1475</v>
+        <v>3.0498</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1475</v>
+        <v>3.4217</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0.3719</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1475</v>
+        <v>3.4217</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1475</v>
+        <v>3.4217</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0.3719</v>
       </c>
       <c r="K4" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M4" t="n">
-        <v>2.1475</v>
+        <v>3.0498</v>
       </c>
       <c r="N4" t="n">
-        <v>138</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>buster</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.8597</v>
+        <v>2.8931</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3152</v>
+        <v>0.4903</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3299</v>
+        <v>0.7087</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8597</v>
+        <v>2.8931</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2316</v>
+        <v>2.8931</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3719</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2316</v>
+        <v>2.8931</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2316</v>
+        <v>2.8931</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3719</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="L5" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.8597</v>
+        <v>2.8931</v>
       </c>
       <c r="N5" t="n">
-        <v>219</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.7565</v>
+        <v>2.5516</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2977</v>
+        <v>0.4325</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2882</v>
+        <v>0.5726</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7565</v>
+        <v>2.5516</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6164</v>
+        <v>2.5516</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8599</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6164</v>
+        <v>2.5516</v>
       </c>
       <c r="I6" t="n">
-        <v>2.6164</v>
+        <v>2.5516</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8599</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="L6" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.7565</v>
+        <v>2.5516</v>
       </c>
       <c r="N6" t="n">
-        <v>207</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.7071</v>
+        <v>2.4159</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2893</v>
+        <v>0.4095</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2683</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7071</v>
+        <v>2.4159</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7071</v>
+        <v>3.2758</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0.8599</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7071</v>
+        <v>3.2758</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7071</v>
+        <v>3.2758</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0.8599</v>
       </c>
       <c r="K7" t="n">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M7" t="n">
-        <v>1.7071</v>
+        <v>2.4159</v>
       </c>
       <c r="N7" t="n">
-        <v>138</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.6198</v>
+        <v>2.1122</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2745</v>
+        <v>0.358</v>
       </c>
       <c r="D8" t="n">
-        <v>0.233</v>
+        <v>0.3976</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6198</v>
+        <v>2.1122</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6198</v>
+        <v>2.1122</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6198</v>
+        <v>2.1122</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6198</v>
+        <v>2.1122</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.6198</v>
+        <v>2.1122</v>
       </c>
       <c r="N8" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.4802</v>
+        <v>2.1044</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2509</v>
+        <v>0.3567</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1766</v>
+        <v>0.3945</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4802</v>
+        <v>2.1044</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4802</v>
+        <v>2.1044</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4802</v>
+        <v>2.1044</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4802</v>
+        <v>2.1044</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.4802</v>
+        <v>2.1044</v>
       </c>
       <c r="N9" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>facecrack</t>
+          <t>xsepower</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.1901</v>
+        <v>1.9488</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2017</v>
+        <v>0.3303</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0594</v>
+        <v>0.3325</v>
       </c>
       <c r="E10" t="n">
-        <v>1.1901</v>
+        <v>1.9488</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9949</v>
+        <v>1.5058</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1952</v>
+        <v>0.443</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9949</v>
+        <v>1.5058</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9949</v>
+        <v>1.5058</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1952</v>
+        <v>0.443</v>
       </c>
       <c r="K10" t="n">
         <v>128</v>
@@ -897,7 +897,7 @@
         <v>79</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1901</v>
+        <v>1.9488</v>
       </c>
       <c r="N10" t="n">
         <v>207</v>
@@ -906,35 +906,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>xsepower</t>
+          <t>almazer</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.0984</v>
+        <v>1.7381</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1862</v>
+        <v>0.2946</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0224</v>
+        <v>0.2485</v>
       </c>
       <c r="E11" t="n">
-        <v>1.0984</v>
+        <v>1.7381</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6554</v>
+        <v>1.3819</v>
       </c>
       <c r="G11" t="n">
-        <v>0.443</v>
+        <v>0.3562</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6554</v>
+        <v>1.3819</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6554</v>
+        <v>1.3819</v>
       </c>
       <c r="J11" t="n">
-        <v>0.443</v>
+        <v>0.3562</v>
       </c>
       <c r="K11" t="n">
         <v>128</v>
@@ -943,7 +943,7 @@
         <v>79</v>
       </c>
       <c r="M11" t="n">
-        <v>1.0984</v>
+        <v>1.7381</v>
       </c>
       <c r="N11" t="n">
         <v>207</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>facecrack</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9205</v>
+        <v>1.7378</v>
       </c>
       <c r="C12" t="n">
-        <v>0.156</v>
+        <v>0.2945</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0495</v>
+        <v>0.2484</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9205</v>
+        <v>1.7378</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9205</v>
+        <v>1.5426</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9205</v>
+        <v>1.5426</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9205</v>
+        <v>1.5426</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="K12" t="n">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9205</v>
+        <v>1.7378</v>
       </c>
       <c r="N12" t="n">
-        <v>137</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>almazer</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8074</v>
+        <v>0.9205</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1368</v>
+        <v>0.156</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-0.0772</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8074</v>
+        <v>0.9205</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4512</v>
+        <v>0.9205</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3562</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4512</v>
+        <v>0.9205</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4512</v>
+        <v>0.9205</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3562</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="L13" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8074</v>
+        <v>0.9205</v>
       </c>
       <c r="N13" t="n">
-        <v>207</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14">
@@ -1054,7 +1054,7 @@
         <v>0.1053</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1705</v>
+        <v>-0.1965</v>
       </c>
       <c r="E14" t="n">
         <v>0.6211</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Plopski</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3526</v>
+        <v>0.4435</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0598</v>
+        <v>0.0752</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2789</v>
+        <v>-0.2672</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3526</v>
+        <v>0.4435</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3526</v>
+        <v>1.1211</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.6776</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3526</v>
+        <v>1.1211</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3526</v>
+        <v>1.1211</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.6776</v>
       </c>
       <c r="K15" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3526</v>
+        <v>0.4435</v>
       </c>
       <c r="N15" t="n">
-        <v>137</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>Plopski</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1805</v>
+        <v>0.3526</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0306</v>
+        <v>0.0598</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3484</v>
+        <v>-0.3034</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1805</v>
+        <v>0.3526</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8581</v>
+        <v>0.3526</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6776</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8581</v>
+        <v>0.3526</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8581</v>
+        <v>0.3526</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6776</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="L16" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1805</v>
+        <v>0.3526</v>
       </c>
       <c r="N16" t="n">
-        <v>219</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17">
@@ -1192,7 +1192,7 @@
         <v>-0.0297</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4921</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="E17" t="n">
         <v>-0.175</v>
@@ -1228,216 +1228,216 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>sergej</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.3492</v>
+        <v>-0.2766</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.0592</v>
+        <v>-0.0469</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5624</v>
+        <v>-0.5541</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3492</v>
+        <v>-0.2766</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3492</v>
+        <v>-0.2766</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3492</v>
+        <v>-0.2766</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3492</v>
+        <v>-0.2766</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3492</v>
+        <v>-0.2766</v>
       </c>
       <c r="N18" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SANJI</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.7079</v>
+        <v>-0.3492</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.12</v>
+        <v>-0.0592</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7073</v>
+        <v>-0.583</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7079</v>
+        <v>-0.3492</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6881</v>
+        <v>-0.3492</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9802</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6881</v>
+        <v>-0.3492</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6881</v>
+        <v>-0.3492</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9802</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="L19" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7079</v>
+        <v>-0.3492</v>
       </c>
       <c r="N19" t="n">
-        <v>219</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>SANJI</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.7836</v>
+        <v>-0.7079</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.1328</v>
+        <v>-0.12</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7379</v>
+        <v>-0.7259</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7836</v>
+        <v>-0.7079</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7836</v>
+        <v>-1.6881</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.9802</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7836</v>
+        <v>-1.6881</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7836</v>
+        <v>-1.6881</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.9802</v>
       </c>
       <c r="K20" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7836</v>
+        <v>-0.7079</v>
       </c>
       <c r="N20" t="n">
-        <v>138</v>
+        <v>219</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.8293</v>
+        <v>-0.7836</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.1406</v>
+        <v>-0.1328</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7564</v>
+        <v>-0.7561</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8293</v>
+        <v>-0.7836</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8293</v>
+        <v>-0.7836</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8293</v>
+        <v>-0.7836</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8293</v>
+        <v>-0.7836</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8293</v>
+        <v>-0.7836</v>
       </c>
       <c r="N21" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>sergej</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.971</v>
+        <v>-0.8245</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.1646</v>
+        <v>-0.1397</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8136</v>
+        <v>-0.7724</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.971</v>
+        <v>-0.8245</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.971</v>
+        <v>-0.8245</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.971</v>
+        <v>-0.8245</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.971</v>
+        <v>-0.8245</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.971</v>
+        <v>-0.8245</v>
       </c>
       <c r="N22" t="n">
         <v>133</v>
@@ -1468,7 +1468,7 @@
         <v>-0.1819</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8548</v>
+        <v>-0.8714</v>
       </c>
       <c r="E23" t="n">
         <v>-1.073</v>
@@ -1514,7 +1514,7 @@
         <v>-0.1937</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8829</v>
+        <v>-0.8991</v>
       </c>
       <c r="E24" t="n">
         <v>-1.1426</v>
@@ -1560,7 +1560,7 @@
         <v>-0.1983</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.894</v>
+        <v>-0.91</v>
       </c>
       <c r="E25" t="n">
         <v>-1.17</v>
@@ -1606,7 +1606,7 @@
         <v>-0.2083</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.9179</v>
+        <v>-0.9336</v>
       </c>
       <c r="E26" t="n">
         <v>-1.2291</v>
@@ -1652,7 +1652,7 @@
         <v>-0.2095</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.9207</v>
+        <v>-0.9363</v>
       </c>
       <c r="E27" t="n">
         <v>-1.236</v>
@@ -1698,7 +1698,7 @@
         <v>-0.225</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.9576</v>
+        <v>-0.9728</v>
       </c>
       <c r="E28" t="n">
         <v>-1.3275</v>
@@ -1744,7 +1744,7 @@
         <v>-0.2608</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.043</v>
+        <v>-1.057</v>
       </c>
       <c r="E29" t="n">
         <v>-1.5388</v>
@@ -1790,7 +1790,7 @@
         <v>-0.2945</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.1232</v>
+        <v>-1.1361</v>
       </c>
       <c r="E30" t="n">
         <v>-1.7373</v>
@@ -1836,7 +1836,7 @@
         <v>-0.333</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.2151</v>
+        <v>-1.2267</v>
       </c>
       <c r="E31" t="n">
         <v>-1.9648</v>

--- a/database/event/4686/event_4686_evp_summary.xlsx
+++ b/database/event/4686/event_4686_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.1303</v>
+        <v>6.2799</v>
       </c>
       <c r="C2" t="n">
-        <v>1.2085</v>
+        <v>1.0644</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3968</v>
+        <v>2.197</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1303</v>
+        <v>6.2799</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7816</v>
+        <v>3.3773</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3487</v>
+        <v>2.9026</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7816</v>
+        <v>4.0561</v>
       </c>
       <c r="I2" t="n">
-        <v>3.7816</v>
+        <v>4.0561</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3487</v>
+        <v>2.9026</v>
       </c>
       <c r="K2" t="n">
         <v>140</v>
@@ -529,7 +529,7 @@
         <v>79</v>
       </c>
       <c r="M2" t="n">
-        <v>7.1303</v>
+        <v>6.9587</v>
       </c>
       <c r="N2" t="n">
         <v>219</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.6</v>
+        <v>3.917</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6102</v>
+        <v>0.6639</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9903</v>
+        <v>1.1303</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6</v>
+        <v>3.917</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5174</v>
+        <v>2.6528</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0826</v>
+        <v>1.2642</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5174</v>
+        <v>2.6528</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5174</v>
+        <v>2.6528</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0826</v>
+        <v>1.2642</v>
       </c>
       <c r="K3" t="n">
         <v>128</v>
@@ -575,7 +575,7 @@
         <v>79</v>
       </c>
       <c r="M3" t="n">
-        <v>3.6</v>
+        <v>3.917</v>
       </c>
       <c r="N3" t="n">
         <v>207</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.0498</v>
+        <v>2.8939</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5169</v>
+        <v>0.4905</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7711</v>
+        <v>0.6684</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0498</v>
+        <v>2.8939</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4217</v>
+        <v>3.153</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3719</v>
+        <v>-0.2591</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4217</v>
+        <v>3.5637</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4217</v>
+        <v>3.5637</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.3719</v>
+        <v>-0.2591</v>
       </c>
       <c r="K4" t="n">
         <v>140</v>
@@ -621,7 +621,7 @@
         <v>79</v>
       </c>
       <c r="M4" t="n">
-        <v>3.0498</v>
+        <v>3.3046</v>
       </c>
       <c r="N4" t="n">
         <v>219</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.8931</v>
+        <v>2.8442</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4903</v>
+        <v>0.4821</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7087</v>
+        <v>0.646</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8931</v>
+        <v>2.8442</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8931</v>
+        <v>2.8442</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8931</v>
+        <v>2.8856</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8931</v>
+        <v>2.8856</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8931</v>
+        <v>2.8856</v>
       </c>
       <c r="N5" t="n">
         <v>137</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.5516</v>
+        <v>2.7567</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4325</v>
+        <v>0.4672</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5726</v>
+        <v>0.6065</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5516</v>
+        <v>2.7567</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5516</v>
+        <v>2.7567</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5516</v>
+        <v>2.7567</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5516</v>
+        <v>2.7567</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.5516</v>
+        <v>2.7567</v>
       </c>
       <c r="N6" t="n">
         <v>138</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.4159</v>
+        <v>2.7512</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4095</v>
+        <v>0.4663</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.604</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4159</v>
+        <v>2.7512</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2758</v>
+        <v>3.0756</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8599</v>
+        <v>-0.3244</v>
       </c>
       <c r="H7" t="n">
-        <v>3.2758</v>
+        <v>3.3938</v>
       </c>
       <c r="I7" t="n">
-        <v>3.2758</v>
+        <v>3.3938</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8599</v>
+        <v>-0.3244</v>
       </c>
       <c r="K7" t="n">
         <v>128</v>
@@ -759,7 +759,7 @@
         <v>79</v>
       </c>
       <c r="M7" t="n">
-        <v>2.4159</v>
+        <v>3.0694</v>
       </c>
       <c r="N7" t="n">
         <v>207</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.1122</v>
+        <v>2.5617</v>
       </c>
       <c r="C8" t="n">
-        <v>0.358</v>
+        <v>0.4342</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3976</v>
+        <v>0.5185</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1122</v>
+        <v>2.5617</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1122</v>
+        <v>2.5617</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.1122</v>
+        <v>2.5617</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1122</v>
+        <v>2.5617</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.1122</v>
+        <v>2.5617</v>
       </c>
       <c r="N8" t="n">
         <v>138</v>
@@ -814,127 +814,127 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>xsepower</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.1044</v>
+        <v>2.2831</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3567</v>
+        <v>0.387</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3945</v>
+        <v>0.3927</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1044</v>
+        <v>2.2831</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1044</v>
+        <v>1.6474</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.6357</v>
       </c>
       <c r="H9" t="n">
-        <v>2.1044</v>
+        <v>1.6474</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1044</v>
+        <v>1.6474</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.6357</v>
       </c>
       <c r="K9" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M9" t="n">
-        <v>2.1044</v>
+        <v>2.2831</v>
       </c>
       <c r="N9" t="n">
-        <v>133</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>xsepower</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.9488</v>
+        <v>2.2256</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3303</v>
+        <v>0.3772</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3325</v>
+        <v>0.3667</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9488</v>
+        <v>2.2256</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5058</v>
+        <v>2.2256</v>
       </c>
       <c r="G10" t="n">
-        <v>0.443</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5058</v>
+        <v>2.2256</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5058</v>
+        <v>2.2256</v>
       </c>
       <c r="J10" t="n">
-        <v>0.443</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="L10" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.9488</v>
+        <v>2.2256</v>
       </c>
       <c r="N10" t="n">
-        <v>207</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>almazer</t>
+          <t>facecrack</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.7381</v>
+        <v>2.1311</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2946</v>
+        <v>0.3612</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2485</v>
+        <v>0.3241</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7381</v>
+        <v>2.1311</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3819</v>
+        <v>1.7213</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3562</v>
+        <v>0.4098</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3819</v>
+        <v>1.7213</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3819</v>
+        <v>1.7213</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3562</v>
+        <v>0.4098</v>
       </c>
       <c r="K11" t="n">
         <v>128</v>
@@ -943,7 +943,7 @@
         <v>79</v>
       </c>
       <c r="M11" t="n">
-        <v>1.7381</v>
+        <v>2.1311</v>
       </c>
       <c r="N11" t="n">
         <v>207</v>
@@ -952,35 +952,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>facecrack</t>
+          <t>almazer</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.7378</v>
+        <v>2.0208</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2945</v>
+        <v>0.3425</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2484</v>
+        <v>0.2743</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7378</v>
+        <v>2.0208</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5426</v>
+        <v>1.6476</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1952</v>
+        <v>0.3732</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5426</v>
+        <v>1.6476</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5426</v>
+        <v>1.6476</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1952</v>
+        <v>0.3732</v>
       </c>
       <c r="K12" t="n">
         <v>128</v>
@@ -989,7 +989,7 @@
         <v>79</v>
       </c>
       <c r="M12" t="n">
-        <v>1.7378</v>
+        <v>2.0208</v>
       </c>
       <c r="N12" t="n">
         <v>207</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9205</v>
+        <v>1.138</v>
       </c>
       <c r="C13" t="n">
-        <v>0.156</v>
+        <v>0.1929</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0772</v>
+        <v>-0.1243</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9205</v>
+        <v>1.138</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9205</v>
+        <v>1.138</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9205</v>
+        <v>1.138</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9205</v>
+        <v>1.138</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9205</v>
+        <v>1.138</v>
       </c>
       <c r="N13" t="n">
         <v>137</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6211</v>
+        <v>0.9154</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1053</v>
+        <v>0.1551</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1965</v>
+        <v>-0.2248</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6211</v>
+        <v>0.9154</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6211</v>
+        <v>0.9154</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6211</v>
+        <v>0.9154</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6211</v>
+        <v>0.9154</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6211</v>
+        <v>0.9154</v>
       </c>
       <c r="N14" t="n">
         <v>134</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4435</v>
+        <v>0.8693</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0752</v>
+        <v>0.1473</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2672</v>
+        <v>-0.2456</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4435</v>
+        <v>0.8693</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1211</v>
+        <v>1.3899</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6776</v>
+        <v>-0.5206</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1211</v>
+        <v>1.3899</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1211</v>
+        <v>1.3899</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6776</v>
+        <v>-0.5206</v>
       </c>
       <c r="K15" t="n">
         <v>140</v>
@@ -1127,7 +1127,7 @@
         <v>79</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4435</v>
+        <v>0.8693</v>
       </c>
       <c r="N15" t="n">
         <v>219</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3526</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0598</v>
+        <v>0.1289</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3034</v>
+        <v>-0.2946</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3526</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3526</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3526</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3526</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3526</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="N16" t="n">
         <v>137</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.175</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0297</v>
+        <v>0.0857</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.4098</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.175</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.175</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.175</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.175</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.175</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="N17" t="n">
         <v>133</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.2766</v>
+        <v>0.1478</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.0469</v>
+        <v>0.0251</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5541</v>
+        <v>-0.5713</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2766</v>
+        <v>0.1478</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2766</v>
+        <v>0.1478</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2766</v>
+        <v>0.1478</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2766</v>
+        <v>0.1478</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2766</v>
+        <v>0.1478</v>
       </c>
       <c r="N18" t="n">
         <v>133</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.3492</v>
+        <v>0.0571</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0592</v>
+        <v>0.0097</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.583</v>
+        <v>-0.6122</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3492</v>
+        <v>0.0571</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3492</v>
+        <v>0.0571</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3492</v>
+        <v>0.0571</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3492</v>
+        <v>0.0571</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3492</v>
+        <v>0.0571</v>
       </c>
       <c r="N19" t="n">
         <v>134</v>
@@ -1320,139 +1320,139 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SANJI</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.7079</v>
+        <v>-0.2666</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.12</v>
+        <v>-0.0452</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7259</v>
+        <v>-0.7584</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7079</v>
+        <v>-0.2666</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6881</v>
+        <v>-0.2666</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9802</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6881</v>
+        <v>-0.2666</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.6881</v>
+        <v>-0.2666</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9802</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L20" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7079</v>
+        <v>-0.2666</v>
       </c>
       <c r="N20" t="n">
-        <v>219</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.7836</v>
+        <v>-0.2936</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.1328</v>
+        <v>-0.0498</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7561</v>
+        <v>-0.7706</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7836</v>
+        <v>-0.2936</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7836</v>
+        <v>-0.2936</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7836</v>
+        <v>-0.2936</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7836</v>
+        <v>-0.2936</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7836</v>
+        <v>-0.2936</v>
       </c>
       <c r="N21" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>SANJI</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.8245</v>
+        <v>-0.3277</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.1397</v>
+        <v>-0.0555</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7724</v>
+        <v>-0.786</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8245</v>
+        <v>-0.3277</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8245</v>
+        <v>-1.243</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.9153</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8245</v>
+        <v>-1.243</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8245</v>
+        <v>-1.243</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.9153</v>
       </c>
       <c r="K22" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8245</v>
+        <v>-0.3277000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>133</v>
+        <v>219</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-1.073</v>
+        <v>-0.5434</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.1819</v>
+        <v>-0.0921</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8714</v>
+        <v>-0.8833</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.073</v>
+        <v>-0.5434</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.073</v>
+        <v>-0.5434</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.073</v>
+        <v>-0.5434</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.073</v>
+        <v>-0.5434</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.073</v>
+        <v>-0.5434</v>
       </c>
       <c r="N23" t="n">
         <v>134</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-1.1426</v>
+        <v>-0.648</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1937</v>
+        <v>-0.1098</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8991</v>
+        <v>-0.9306</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1426</v>
+        <v>-0.648</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1426</v>
+        <v>-0.648</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.1426</v>
+        <v>-0.648</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.1426</v>
+        <v>-0.648</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1426</v>
+        <v>-0.648</v>
       </c>
       <c r="N24" t="n">
         <v>137</v>
@@ -1550,170 +1550,170 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-1.17</v>
+        <v>-0.6573</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1983</v>
+        <v>-0.1114</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.91</v>
+        <v>-0.9348</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.17</v>
+        <v>-0.6573</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.17</v>
+        <v>-0.6573</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.17</v>
+        <v>-0.6573</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.17</v>
+        <v>-0.6573</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.17</v>
+        <v>-0.6573</v>
       </c>
       <c r="N25" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Qikert</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1.2291</v>
+        <v>-0.6937</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.2083</v>
+        <v>-0.1176</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.9336</v>
+        <v>-0.9512</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.2291</v>
+        <v>-0.6937</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.2291</v>
+        <v>-0.6937</v>
       </c>
       <c r="G26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2291</v>
+        <v>-0.6937</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2291</v>
+        <v>-0.6937</v>
       </c>
       <c r="J26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L26" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.2291</v>
+        <v>-0.6937</v>
       </c>
       <c r="N26" t="n">
-        <v>219</v>
+        <v>138</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>Qikert</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.236</v>
+        <v>-0.8414</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.2095</v>
+        <v>-0.1426</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.9363</v>
+        <v>-1.0179</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.236</v>
+        <v>-0.8414</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.236</v>
+        <v>0.1586</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.236</v>
+        <v>0.1586</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.236</v>
+        <v>0.1586</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K27" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.236</v>
+        <v>-0.8414</v>
       </c>
       <c r="N27" t="n">
-        <v>134</v>
+        <v>219</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.3275</v>
+        <v>-0.8502</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.225</v>
+        <v>-0.1441</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.9728</v>
+        <v>-1.0218</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.3275</v>
+        <v>-0.8502</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.3275</v>
+        <v>-0.8502</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.3275</v>
+        <v>-0.8502</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.3275</v>
+        <v>-0.8502</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.3275</v>
+        <v>-0.8502</v>
       </c>
       <c r="N28" t="n">
         <v>134</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.5388</v>
+        <v>-1.1697</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2608</v>
+        <v>-0.1982</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.057</v>
+        <v>-1.1661</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.5388</v>
+        <v>-1.1697</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.5388</v>
+        <v>-1.1697</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.5388</v>
+        <v>-1.1697</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.5388</v>
+        <v>-1.1697</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.5388</v>
+        <v>-1.1697</v>
       </c>
       <c r="N29" t="n">
         <v>137</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.7373</v>
+        <v>-1.462</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2945</v>
+        <v>-0.2478</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.1361</v>
+        <v>-1.298</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.7373</v>
+        <v>-1.462</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.7373</v>
+        <v>-1.462</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.7373</v>
+        <v>-1.462</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.7373</v>
+        <v>-1.462</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.7373</v>
+        <v>-1.462</v>
       </c>
       <c r="N30" t="n">
         <v>138</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.9648</v>
+        <v>-1.6671</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.333</v>
+        <v>-0.2826</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.2267</v>
+        <v>-1.3906</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.9648</v>
+        <v>-1.6671</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.9648</v>
+        <v>-1.6671</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.9648</v>
+        <v>-1.6671</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.9648</v>
+        <v>-1.6671</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.9648</v>
+        <v>-1.6671</v>
       </c>
       <c r="N31" t="n">
         <v>133</v>
@@ -1969,10 +1969,10 @@
         <v>1.3</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4734</v>
+        <v>0.5727</v>
       </c>
       <c r="J2" t="n">
-        <v>13.7286</v>
+        <v>16.6083</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.27</v>
       </c>
       <c r="I3" t="n">
-        <v>0.433</v>
+        <v>0.5226</v>
       </c>
       <c r="J3" t="n">
-        <v>12.557</v>
+        <v>15.1554</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>1.11</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1717</v>
+        <v>0.2421</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9793</v>
+        <v>7.0209</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>1.09</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1364</v>
+        <v>0.2027</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9556</v>
+        <v>5.8783</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.95</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1773</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>-5.1417</v>
+        <v>-2.6332</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.51</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3804</v>
+        <v>1.2431</v>
       </c>
       <c r="J7" t="n">
-        <v>40.0316</v>
+        <v>36.0499</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>0.92</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2981</v>
+        <v>-0.2763</v>
       </c>
       <c r="J8" t="n">
-        <v>-8.6449</v>
+        <v>-8.012700000000001</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6186</v>
+        <v>-0.5789</v>
       </c>
       <c r="J9" t="n">
-        <v>-17.9394</v>
+        <v>-16.7881</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6186</v>
+        <v>-0.5789</v>
       </c>
       <c r="J10" t="n">
-        <v>-17.9394</v>
+        <v>-16.7881</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9106</v>
+        <v>-0.8827</v>
       </c>
       <c r="J11" t="n">
-        <v>-26.4074</v>
+        <v>-25.5983</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.4</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6119</v>
+        <v>0.5321</v>
       </c>
       <c r="J12" t="n">
-        <v>17.1332</v>
+        <v>14.8988</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.32</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5117</v>
+        <v>0.4386</v>
       </c>
       <c r="J13" t="n">
-        <v>14.3276</v>
+        <v>12.2808</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>1.15</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2686</v>
+        <v>0.2283</v>
       </c>
       <c r="J14" t="n">
-        <v>7.5208</v>
+        <v>6.3924</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>0.88</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2874</v>
+        <v>-0.1678</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.0472</v>
+        <v>-4.6984</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.78</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4324</v>
+        <v>-0.2705</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.1072</v>
+        <v>-7.574</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.07</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1936</v>
+        <v>0.1497</v>
       </c>
       <c r="J17" t="n">
-        <v>5.4208</v>
+        <v>4.1916</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>0.99</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0057</v>
+        <v>-0.0168</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1596</v>
+        <v>-0.4704</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>0.95</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1086</v>
+        <v>-0.0718</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.0408</v>
+        <v>-2.0104</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.88</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2455</v>
+        <v>-0.1507</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.874</v>
+        <v>-4.2196</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.87</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2623</v>
+        <v>-0.1614</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.3444</v>
+        <v>-4.5192</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.4</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6776</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>14.9072</v>
+        <v>18.3304</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.13</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3109</v>
+        <v>0.3355</v>
       </c>
       <c r="J23" t="n">
-        <v>6.8398</v>
+        <v>7.381</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>0.95</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0784</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.7248</v>
+        <v>-1.4982</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>0.7</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5017</v>
+        <v>-0.3255</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.0374</v>
+        <v>-7.161</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.37</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.9009</v>
+        <v>-0.6266</v>
       </c>
       <c r="J26" t="n">
-        <v>-19.8198</v>
+        <v>-13.7852</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>1.82</v>
       </c>
       <c r="I27" t="n">
-        <v>1.7747</v>
+        <v>1.5098</v>
       </c>
       <c r="J27" t="n">
-        <v>39.0434</v>
+        <v>33.2156</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>1.68</v>
       </c>
       <c r="I28" t="n">
-        <v>1.5238</v>
+        <v>1.3423</v>
       </c>
       <c r="J28" t="n">
-        <v>33.5236</v>
+        <v>29.5306</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>1.12</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2524</v>
+        <v>0.3366</v>
       </c>
       <c r="J29" t="n">
-        <v>5.5528</v>
+        <v>7.4052</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>1.05</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0496</v>
+        <v>0.1301</v>
       </c>
       <c r="J30" t="n">
-        <v>1.0912</v>
+        <v>2.8622</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.79</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7735</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>-17.017</v>
+        <v>-15.8686</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.05</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2103</v>
+        <v>0.1989</v>
       </c>
       <c r="J32" t="n">
-        <v>6.0987</v>
+        <v>5.7681</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.02</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1475</v>
+        <v>0.1204</v>
       </c>
       <c r="J33" t="n">
-        <v>4.2775</v>
+        <v>3.4916</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>0.8</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.318</v>
+        <v>-0.2169</v>
       </c>
       <c r="J34" t="n">
-        <v>-9.222</v>
+        <v>-6.2901</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4896</v>
+        <v>-0.3223</v>
       </c>
       <c r="J35" t="n">
-        <v>-14.1984</v>
+        <v>-9.3467</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.52</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.713</v>
+        <v>-0.4811</v>
       </c>
       <c r="J36" t="n">
-        <v>-20.677</v>
+        <v>-13.9519</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.42</v>
       </c>
       <c r="I37" t="n">
-        <v>1.058</v>
+        <v>1.0364</v>
       </c>
       <c r="J37" t="n">
-        <v>30.682</v>
+        <v>30.0556</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.41</v>
       </c>
       <c r="I38" t="n">
-        <v>1.0368</v>
+        <v>1.0214</v>
       </c>
       <c r="J38" t="n">
-        <v>30.0672</v>
+        <v>29.6206</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.29</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7682</v>
+        <v>0.7705</v>
       </c>
       <c r="J39" t="n">
-        <v>22.2778</v>
+        <v>22.3445</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>1.06</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1156</v>
+        <v>0.1841</v>
       </c>
       <c r="J40" t="n">
-        <v>3.3524</v>
+        <v>5.3389</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.82</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.6231</v>
       </c>
       <c r="J41" t="n">
-        <v>-19.778</v>
+        <v>-18.0699</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>0.95</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.017</v>
+        <v>-0.0442</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.425</v>
+        <v>-1.105</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>0.91</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.0914</v>
+        <v>-0.0944</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.285</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.4745</v>
+        <v>-0.3163</v>
       </c>
       <c r="J44" t="n">
-        <v>-11.8625</v>
+        <v>-7.9075</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>0.68</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4892</v>
+        <v>-0.3257</v>
       </c>
       <c r="J45" t="n">
-        <v>-12.23</v>
+        <v>-8.1425</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>0.64</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5462</v>
+        <v>-0.3634</v>
       </c>
       <c r="J46" t="n">
-        <v>-13.655</v>
+        <v>-9.085000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>2.14</v>
       </c>
       <c r="I47" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J47" t="n">
-        <v>51.4825</v>
+        <v>45.845</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.24</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5585</v>
+        <v>0.6383</v>
       </c>
       <c r="J48" t="n">
-        <v>13.9625</v>
+        <v>15.9575</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>1.24</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5585</v>
+        <v>0.6383</v>
       </c>
       <c r="J49" t="n">
-        <v>13.9625</v>
+        <v>15.9575</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.96</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3245</v>
+        <v>-0.2402</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.112500000000001</v>
+        <v>-6.005</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.9</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5018</v>
+        <v>-0.4262</v>
       </c>
       <c r="J51" t="n">
-        <v>-12.545</v>
+        <v>-10.655</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.33</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5657</v>
+        <v>0.6773</v>
       </c>
       <c r="J52" t="n">
-        <v>14.1425</v>
+        <v>16.9325</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.08</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2007</v>
+        <v>0.2098</v>
       </c>
       <c r="J53" t="n">
-        <v>5.0175</v>
+        <v>5.245</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0156</v>
+        <v>0.0025</v>
       </c>
       <c r="J54" t="n">
-        <v>0.39</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>0.78</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4075</v>
+        <v>-0.2566</v>
       </c>
       <c r="J55" t="n">
-        <v>-10.1875</v>
+        <v>-6.415</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.71</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5033</v>
+        <v>-0.3245</v>
       </c>
       <c r="J56" t="n">
-        <v>-12.5825</v>
+        <v>-8.112500000000001</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9252</v>
+        <v>0.9113</v>
       </c>
       <c r="J57" t="n">
-        <v>23.13</v>
+        <v>22.7825</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>1.13</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3901</v>
+        <v>0.3986</v>
       </c>
       <c r="J58" t="n">
-        <v>9.7525</v>
+        <v>9.965</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>1.11</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3154</v>
+        <v>0.3465</v>
       </c>
       <c r="J59" t="n">
-        <v>7.885</v>
+        <v>8.6625</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>1.1</v>
       </c>
       <c r="I60" t="n">
-        <v>0.283</v>
+        <v>0.3193</v>
       </c>
       <c r="J60" t="n">
-        <v>7.075</v>
+        <v>7.9825</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3328</v>
+        <v>-0.2629</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.32</v>
+        <v>-6.5725</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>0.89</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.1182</v>
+        <v>-0.1139</v>
       </c>
       <c r="J62" t="n">
-        <v>-2.8368</v>
+        <v>-2.7336</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>0.82</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.236</v>
+        <v>-0.1902</v>
       </c>
       <c r="J63" t="n">
-        <v>-5.664</v>
+        <v>-4.5648</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>0.79</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2866</v>
+        <v>-0.2204</v>
       </c>
       <c r="J64" t="n">
-        <v>-6.8784</v>
+        <v>-5.2896</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.71</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.4359</v>
+        <v>-0.2949</v>
       </c>
       <c r="J65" t="n">
-        <v>-10.4616</v>
+        <v>-7.0776</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.57</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.4262</v>
       </c>
       <c r="J66" t="n">
-        <v>-15.2544</v>
+        <v>-10.2288</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.69</v>
       </c>
       <c r="I67" t="n">
-        <v>1.544</v>
+        <v>1.3555</v>
       </c>
       <c r="J67" t="n">
-        <v>37.056</v>
+        <v>32.532</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.57</v>
       </c>
       <c r="I68" t="n">
-        <v>1.3179</v>
+        <v>1.2092</v>
       </c>
       <c r="J68" t="n">
-        <v>31.6296</v>
+        <v>29.0208</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>1.28</v>
       </c>
       <c r="I69" t="n">
-        <v>0.6688</v>
+        <v>0.7309</v>
       </c>
       <c r="J69" t="n">
-        <v>16.0512</v>
+        <v>17.5416</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>1.26</v>
       </c>
       <c r="I70" t="n">
-        <v>0.6146</v>
+        <v>0.6861</v>
       </c>
       <c r="J70" t="n">
-        <v>14.7504</v>
+        <v>16.4664</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.64</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.0966</v>
+        <v>-1.0849</v>
       </c>
       <c r="J71" t="n">
-        <v>-26.3184</v>
+        <v>-26.0376</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.12</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3924</v>
+        <v>0.4469</v>
       </c>
       <c r="J72" t="n">
-        <v>9.81</v>
+        <v>11.1725</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>0.78</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.2618</v>
+        <v>-0.2169</v>
       </c>
       <c r="J73" t="n">
-        <v>-6.545</v>
+        <v>-5.4225</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>0.62</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.539</v>
+        <v>-0.3677</v>
       </c>
       <c r="J74" t="n">
-        <v>-13.475</v>
+        <v>-9.192500000000001</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>0.46</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.7589</v>
+        <v>-0.5173</v>
       </c>
       <c r="J75" t="n">
-        <v>-18.9725</v>
+        <v>-12.9325</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>0.43</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7968</v>
+        <v>-0.5454</v>
       </c>
       <c r="J76" t="n">
-        <v>-19.92</v>
+        <v>-13.635</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>2.22</v>
       </c>
       <c r="I77" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J77" t="n">
-        <v>51.4825</v>
+        <v>45.845</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>1.39</v>
       </c>
       <c r="I78" t="n">
-        <v>0.9147</v>
+        <v>0.9552</v>
       </c>
       <c r="J78" t="n">
-        <v>22.8675</v>
+        <v>23.88</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>1.13</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2604</v>
+        <v>0.352</v>
       </c>
       <c r="J79" t="n">
-        <v>6.51</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>1.04</v>
       </c>
       <c r="I80" t="n">
-        <v>0.0014</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="J80" t="n">
-        <v>0.035</v>
+        <v>2.125</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3995</v>
+        <v>-0.3164</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.987500000000001</v>
+        <v>-7.91</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.14</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3767</v>
+        <v>0.4172</v>
       </c>
       <c r="J82" t="n">
-        <v>8.664099999999999</v>
+        <v>9.595599999999999</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>0.86</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.1829</v>
+        <v>-0.1528</v>
       </c>
       <c r="J83" t="n">
-        <v>-4.2067</v>
+        <v>-3.5144</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>0.78</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.3313</v>
+        <v>-0.2328</v>
       </c>
       <c r="J84" t="n">
-        <v>-7.6199</v>
+        <v>-5.3544</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>0.7</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4637</v>
+        <v>-0.3082</v>
       </c>
       <c r="J85" t="n">
-        <v>-10.6651</v>
+        <v>-7.0886</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.44</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.8044</v>
+        <v>-0.5505</v>
       </c>
       <c r="J86" t="n">
-        <v>-18.5012</v>
+        <v>-12.6615</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.83</v>
       </c>
       <c r="I87" t="n">
-        <v>1.7579</v>
+        <v>1.5008</v>
       </c>
       <c r="J87" t="n">
-        <v>40.4317</v>
+        <v>34.5184</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.56</v>
       </c>
       <c r="I88" t="n">
-        <v>1.2602</v>
+        <v>1.1812</v>
       </c>
       <c r="J88" t="n">
-        <v>28.9846</v>
+        <v>27.1676</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>1.22</v>
       </c>
       <c r="I89" t="n">
-        <v>0.4753</v>
+        <v>0.5754</v>
       </c>
       <c r="J89" t="n">
-        <v>10.9319</v>
+        <v>13.2342</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>1.22</v>
       </c>
       <c r="I90" t="n">
-        <v>0.4753</v>
+        <v>0.5754</v>
       </c>
       <c r="J90" t="n">
-        <v>10.9319</v>
+        <v>13.2342</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>1.02</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.0761</v>
+        <v>0.0074</v>
       </c>
       <c r="J91" t="n">
-        <v>-1.7503</v>
+        <v>0.1702</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.26</v>
       </c>
       <c r="I92" t="n">
-        <v>0.481</v>
+        <v>0.5622</v>
       </c>
       <c r="J92" t="n">
-        <v>13.468</v>
+        <v>15.7416</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>1.03</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1107</v>
+        <v>0.1</v>
       </c>
       <c r="J93" t="n">
-        <v>3.0996</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>0.99</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0098</v>
+        <v>-0.0176</v>
       </c>
       <c r="J94" t="n">
-        <v>-0.2744</v>
+        <v>-0.4928</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.79</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3883</v>
+        <v>-0.2442</v>
       </c>
       <c r="J95" t="n">
-        <v>-10.8724</v>
+        <v>-6.8376</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.73</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4724</v>
+        <v>-0.3029</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.2272</v>
+        <v>-8.481199999999999</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.36</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9692</v>
+        <v>0.9545</v>
       </c>
       <c r="J97" t="n">
-        <v>27.1376</v>
+        <v>26.726</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.2</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5913</v>
+        <v>0.576</v>
       </c>
       <c r="J98" t="n">
-        <v>16.5564</v>
+        <v>16.128</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.06</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1541</v>
+        <v>0.2025</v>
       </c>
       <c r="J99" t="n">
-        <v>4.3148</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>1.03</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0495</v>
+        <v>0.1035</v>
       </c>
       <c r="J100" t="n">
-        <v>1.386</v>
+        <v>2.898</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.97</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2317</v>
+        <v>-0.1623</v>
       </c>
       <c r="J101" t="n">
-        <v>-6.4876</v>
+        <v>-4.5444</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.15</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3185</v>
+        <v>0.3528</v>
       </c>
       <c r="J102" t="n">
-        <v>9.555</v>
+        <v>10.584</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>1.1</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2379</v>
+        <v>0.2532</v>
       </c>
       <c r="J103" t="n">
-        <v>7.137</v>
+        <v>7.596</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>1.05</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1466</v>
+        <v>0.145</v>
       </c>
       <c r="J104" t="n">
-        <v>4.398</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>0.95</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1235</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="J105" t="n">
-        <v>-3.705</v>
+        <v>-2.202</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.62</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6173999999999999</v>
+        <v>-0.4081</v>
       </c>
       <c r="J106" t="n">
-        <v>-18.522</v>
+        <v>-12.243</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.39</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5888</v>
+        <v>0.7201</v>
       </c>
       <c r="J107" t="n">
-        <v>17.664</v>
+        <v>21.603</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.24</v>
       </c>
       <c r="I108" t="n">
-        <v>0.3918</v>
+        <v>0.4723</v>
       </c>
       <c r="J108" t="n">
-        <v>11.754</v>
+        <v>14.169</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>1.2</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3329</v>
+        <v>0.4035</v>
       </c>
       <c r="J109" t="n">
-        <v>9.987</v>
+        <v>12.105</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>0.95</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1769</v>
+        <v>-0.0906</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.307</v>
+        <v>-2.718</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>0.93</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2129</v>
+        <v>-0.115</v>
       </c>
       <c r="J111" t="n">
-        <v>-6.387</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.39</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6218</v>
+        <v>0.7561</v>
       </c>
       <c r="J112" t="n">
-        <v>18.654</v>
+        <v>22.683</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>1.15</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2959</v>
+        <v>0.3354</v>
       </c>
       <c r="J113" t="n">
-        <v>8.877000000000001</v>
+        <v>10.062</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>0.92</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2042</v>
+        <v>-0.1156</v>
       </c>
       <c r="J114" t="n">
-        <v>-6.126</v>
+        <v>-3.468</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>0.88</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2713</v>
+        <v>-0.1602</v>
       </c>
       <c r="J115" t="n">
-        <v>-8.138999999999999</v>
+        <v>-4.806</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.84</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3332</v>
+        <v>-0.2025</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.996</v>
+        <v>-6.075</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.45</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6899</v>
+        <v>0.8499</v>
       </c>
       <c r="J117" t="n">
-        <v>20.697</v>
+        <v>25.497</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.14</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2756</v>
+        <v>0.3136</v>
       </c>
       <c r="J118" t="n">
-        <v>8.268000000000001</v>
+        <v>9.407999999999999</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>0.99</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0631</v>
+        <v>-0.0247</v>
       </c>
       <c r="J119" t="n">
-        <v>-1.893</v>
+        <v>-0.741</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>0.95</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1524</v>
+        <v>-0.0808</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.572</v>
+        <v>-2.424</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.71</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.332</v>
       </c>
       <c r="J121" t="n">
-        <v>-15.468</v>
+        <v>-9.960000000000001</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.32</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.6456</v>
       </c>
       <c r="J122" t="n">
-        <v>16.224</v>
+        <v>19.368</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.19</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3635</v>
+        <v>0.4154</v>
       </c>
       <c r="J123" t="n">
-        <v>10.905</v>
+        <v>12.462</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>1.13</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2716</v>
+        <v>0.302</v>
       </c>
       <c r="J124" t="n">
-        <v>8.148</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>0.75</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4568</v>
+        <v>-0.2901</v>
       </c>
       <c r="J125" t="n">
-        <v>-13.704</v>
+        <v>-8.702999999999999</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.536</v>
+        <v>-0.3475</v>
       </c>
       <c r="J126" t="n">
-        <v>-16.08</v>
+        <v>-10.425</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.4</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6452</v>
+        <v>0.7869</v>
       </c>
       <c r="J127" t="n">
-        <v>19.356</v>
+        <v>23.607</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.03</v>
       </c>
       <c r="I128" t="n">
-        <v>0.0912</v>
+        <v>0.0915</v>
       </c>
       <c r="J128" t="n">
-        <v>2.736</v>
+        <v>2.745</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>0.98</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.06909999999999999</v>
+        <v>-0.0361</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.073</v>
+        <v>-1.083</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3696</v>
+        <v>-0.2292</v>
       </c>
       <c r="J130" t="n">
-        <v>-11.088</v>
+        <v>-6.876</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.79</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3984</v>
+        <v>-0.2492</v>
       </c>
       <c r="J131" t="n">
-        <v>-11.952</v>
+        <v>-7.476</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.43</v>
       </c>
       <c r="I132" t="n">
-        <v>1.1384</v>
+        <v>1.0805</v>
       </c>
       <c r="J132" t="n">
-        <v>34.152</v>
+        <v>32.415</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.22</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.6377</v>
       </c>
       <c r="J133" t="n">
-        <v>19.974</v>
+        <v>19.131</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>0.98</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1755</v>
+        <v>-0.115</v>
       </c>
       <c r="J134" t="n">
-        <v>-5.265</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>0.95</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2841</v>
+        <v>-0.2204</v>
       </c>
       <c r="J135" t="n">
-        <v>-8.523</v>
+        <v>-6.612</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.85</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5726</v>
+        <v>-0.5134</v>
       </c>
       <c r="J136" t="n">
-        <v>-17.178</v>
+        <v>-15.402</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.36</v>
       </c>
       <c r="I137" t="n">
-        <v>0.6055</v>
+        <v>0.7316</v>
       </c>
       <c r="J137" t="n">
-        <v>18.165</v>
+        <v>21.948</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>1.2</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3927</v>
+        <v>0.4474</v>
       </c>
       <c r="J138" t="n">
-        <v>11.781</v>
+        <v>13.422</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>0.92</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.183</v>
+        <v>-0.1089</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.49</v>
+        <v>-3.267</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.76</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4343</v>
+        <v>-0.2755</v>
       </c>
       <c r="J140" t="n">
-        <v>-13.029</v>
+        <v>-8.265000000000001</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.63</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6049</v>
+        <v>-0.3989</v>
       </c>
       <c r="J141" t="n">
-        <v>-18.147</v>
+        <v>-11.967</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.13</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2842</v>
+        <v>0.3113</v>
       </c>
       <c r="J142" t="n">
-        <v>8.526</v>
+        <v>9.339</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.04</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1227</v>
+        <v>0.1197</v>
       </c>
       <c r="J143" t="n">
-        <v>3.681</v>
+        <v>3.591</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>0.95</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1275</v>
+        <v>-0.0742</v>
       </c>
       <c r="J144" t="n">
-        <v>-3.825</v>
+        <v>-2.226</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>0.9</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2219</v>
+        <v>-0.1323</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.657</v>
+        <v>-3.969</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>0.89</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2391</v>
+        <v>-0.1432</v>
       </c>
       <c r="J146" t="n">
-        <v>-7.173</v>
+        <v>-4.296</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>1.54</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7922</v>
+        <v>0.9842</v>
       </c>
       <c r="J147" t="n">
-        <v>23.766</v>
+        <v>29.526</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>1</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.0296</v>
+        <v>-0.0041</v>
       </c>
       <c r="J148" t="n">
-        <v>-0.888</v>
+        <v>-0.123</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>0.96</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1337</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="J149" t="n">
-        <v>-4.011</v>
+        <v>-2.055</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>0.93</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1909</v>
+        <v>-0.1056</v>
       </c>
       <c r="J150" t="n">
-        <v>-5.727</v>
+        <v>-3.168</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.83</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3516</v>
+        <v>-0.2145</v>
       </c>
       <c r="J151" t="n">
-        <v>-10.548</v>
+        <v>-6.435</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.51</v>
       </c>
       <c r="I152" t="n">
-        <v>1.3159</v>
+        <v>1.197</v>
       </c>
       <c r="J152" t="n">
-        <v>36.8452</v>
+        <v>33.516</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>1.06</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2159</v>
+        <v>0.2155</v>
       </c>
       <c r="J153" t="n">
-        <v>6.0452</v>
+        <v>6.034</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>0.99</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1162</v>
+        <v>-0.0668</v>
       </c>
       <c r="J154" t="n">
-        <v>-3.2536</v>
+        <v>-1.8704</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.88</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4815</v>
+        <v>-0.4226</v>
       </c>
       <c r="J155" t="n">
-        <v>-13.482</v>
+        <v>-11.8328</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.85</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5623</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="J156" t="n">
-        <v>-15.7444</v>
+        <v>-14.154</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.4</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6333</v>
+        <v>0.7719</v>
       </c>
       <c r="J157" t="n">
-        <v>17.7324</v>
+        <v>21.6132</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.11</v>
       </c>
       <c r="I158" t="n">
-        <v>0.23</v>
+        <v>0.2577</v>
       </c>
       <c r="J158" t="n">
-        <v>6.44</v>
+        <v>7.2156</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>1.02</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0387</v>
+        <v>0.0615</v>
       </c>
       <c r="J159" t="n">
-        <v>1.0836</v>
+        <v>1.722</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1684</v>
+        <v>-0.0921</v>
       </c>
       <c r="J160" t="n">
-        <v>-4.7152</v>
+        <v>-2.5788</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.72</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5009</v>
+        <v>-0.3214</v>
       </c>
       <c r="J161" t="n">
-        <v>-14.0252</v>
+        <v>-8.9992</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.24</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4503</v>
+        <v>0.5222</v>
       </c>
       <c r="J162" t="n">
-        <v>12.6084</v>
+        <v>14.6216</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>1</v>
       </c>
       <c r="I163" t="n">
-        <v>0.0211</v>
+        <v>0.0042</v>
       </c>
       <c r="J163" t="n">
-        <v>0.5908</v>
+        <v>0.1176</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>1</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0211</v>
+        <v>0.0042</v>
       </c>
       <c r="J164" t="n">
-        <v>0.5908</v>
+        <v>0.1176</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>0.82</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3467</v>
+        <v>-0.2153</v>
       </c>
       <c r="J165" t="n">
-        <v>-9.707599999999999</v>
+        <v>-6.0284</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>0.79</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3908</v>
+        <v>-0.2455</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.9424</v>
+        <v>-6.874</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.47</v>
       </c>
       <c r="I167" t="n">
-        <v>1.2129</v>
+        <v>1.1298</v>
       </c>
       <c r="J167" t="n">
-        <v>33.9612</v>
+        <v>31.6344</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>1.33</v>
       </c>
       <c r="I168" t="n">
-        <v>0.916</v>
+        <v>0.898</v>
       </c>
       <c r="J168" t="n">
-        <v>25.648</v>
+        <v>25.144</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>1.08</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2375</v>
+        <v>0.2675</v>
       </c>
       <c r="J169" t="n">
-        <v>6.65</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>0.9</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4424</v>
+        <v>-0.3772</v>
       </c>
       <c r="J170" t="n">
-        <v>-12.3872</v>
+        <v>-10.5616</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.72</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.8887</v>
+        <v>-0.8519</v>
       </c>
       <c r="J171" t="n">
-        <v>-24.8836</v>
+        <v>-23.8532</v>
       </c>
     </row>
     <row r="172">
@@ -8769,10 +8769,10 @@
         <v>0.64</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.3649</v>
+        <v>-0.3048</v>
       </c>
       <c r="J172" t="n">
-        <v>-7.298</v>
+        <v>-6.096</v>
       </c>
     </row>
     <row r="173">
@@ -8809,10 +8809,10 @@
         <v>0.59</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.4419</v>
+        <v>-0.3578</v>
       </c>
       <c r="J173" t="n">
-        <v>-8.837999999999999</v>
+        <v>-7.156</v>
       </c>
     </row>
     <row r="174">
@@ -8849,10 +8849,10 @@
         <v>0.55</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.5056</v>
+        <v>-0.3982</v>
       </c>
       <c r="J174" t="n">
-        <v>-10.112</v>
+        <v>-7.964</v>
       </c>
     </row>
     <row r="175">
@@ -8889,10 +8889,10 @@
         <v>0.39</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.7896</v>
+        <v>-0.5471</v>
       </c>
       <c r="J175" t="n">
-        <v>-15.792</v>
+        <v>-10.942</v>
       </c>
     </row>
     <row r="176">
@@ -8929,10 +8929,10 @@
         <v>0.29</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.9287</v>
+        <v>-0.6468</v>
       </c>
       <c r="J176" t="n">
-        <v>-18.574</v>
+        <v>-12.936</v>
       </c>
     </row>
     <row r="177">
@@ -8969,10 +8969,10 @@
         <v>2.16</v>
       </c>
       <c r="I177" t="n">
-        <v>2.0593</v>
+        <v>1.8075</v>
       </c>
       <c r="J177" t="n">
-        <v>41.186</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="178">
@@ -9009,10 +9009,10 @@
         <v>1.69</v>
       </c>
       <c r="I178" t="n">
-        <v>1.3877</v>
+        <v>1.2968</v>
       </c>
       <c r="J178" t="n">
-        <v>27.754</v>
+        <v>25.936</v>
       </c>
     </row>
     <row r="179">
@@ -9049,10 +9049,10 @@
         <v>1.58</v>
       </c>
       <c r="I179" t="n">
-        <v>1.1429</v>
+        <v>1.1753</v>
       </c>
       <c r="J179" t="n">
-        <v>22.858</v>
+        <v>23.506</v>
       </c>
     </row>
     <row r="180">
@@ -9089,10 +9089,10 @@
         <v>1.57</v>
       </c>
       <c r="I180" t="n">
-        <v>1.1224</v>
+        <v>1.1639</v>
       </c>
       <c r="J180" t="n">
-        <v>22.448</v>
+        <v>23.278</v>
       </c>
     </row>
     <row r="181">
@@ -9129,10 +9129,10 @@
         <v>1.19</v>
       </c>
       <c r="I181" t="n">
-        <v>0.3306</v>
+        <v>0.4479</v>
       </c>
       <c r="J181" t="n">
-        <v>6.612</v>
+        <v>8.958</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4686/event_4686_evp_summary.xlsx
+++ b/database/event/4686/event_4686_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.2799</v>
+        <v>6.0716</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0644</v>
+        <v>1.0291</v>
       </c>
       <c r="D2" t="n">
-        <v>2.197</v>
+        <v>2.1397</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2799</v>
+        <v>6.0716</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3773</v>
+        <v>3.011</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9026</v>
+        <v>3.0606</v>
       </c>
       <c r="H2" t="n">
-        <v>4.0561</v>
+        <v>3.8653</v>
       </c>
       <c r="I2" t="n">
-        <v>4.0561</v>
+        <v>3.8653</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9026</v>
+        <v>3.0606</v>
       </c>
       <c r="K2" t="n">
         <v>140</v>
@@ -529,7 +529,7 @@
         <v>79</v>
       </c>
       <c r="M2" t="n">
-        <v>6.9587</v>
+        <v>6.9259</v>
       </c>
       <c r="N2" t="n">
         <v>219</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.917</v>
+        <v>3.6549</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6639</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1303</v>
+        <v>1.0396</v>
       </c>
       <c r="E3" t="n">
-        <v>3.917</v>
+        <v>3.6549</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6528</v>
+        <v>2.4097</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2642</v>
+        <v>1.2452</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6528</v>
+        <v>2.5492</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6528</v>
+        <v>2.5492</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2642</v>
+        <v>1.2452</v>
       </c>
       <c r="K3" t="n">
         <v>128</v>
@@ -575,7 +575,7 @@
         <v>79</v>
       </c>
       <c r="M3" t="n">
-        <v>3.917</v>
+        <v>3.7944</v>
       </c>
       <c r="N3" t="n">
         <v>207</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.8939</v>
+        <v>2.6925</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4905</v>
+        <v>0.4563</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6684</v>
+        <v>0.6015</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8939</v>
+        <v>2.6925</v>
       </c>
       <c r="F4" t="n">
-        <v>3.153</v>
+        <v>2.9214</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2591</v>
+        <v>-0.2289</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5637</v>
+        <v>3.669</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5637</v>
+        <v>3.669</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2591</v>
+        <v>-0.2289</v>
       </c>
       <c r="K4" t="n">
         <v>140</v>
@@ -621,7 +621,7 @@
         <v>79</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3046</v>
+        <v>3.4401</v>
       </c>
       <c r="N4" t="n">
         <v>219</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.8442</v>
+        <v>2.6117</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4821</v>
+        <v>0.4427</v>
       </c>
       <c r="D5" t="n">
-        <v>0.646</v>
+        <v>0.5647</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8442</v>
+        <v>2.6117</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8442</v>
+        <v>2.6117</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8856</v>
+        <v>2.9912</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8856</v>
+        <v>2.9912</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8856</v>
+        <v>2.9912</v>
       </c>
       <c r="N5" t="n">
         <v>137</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.7567</v>
+        <v>2.4441</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4672</v>
+        <v>0.4142</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6065</v>
+        <v>0.4884</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7567</v>
+        <v>2.4441</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7567</v>
+        <v>2.4441</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7567</v>
+        <v>2.6244</v>
       </c>
       <c r="I6" t="n">
-        <v>2.7567</v>
+        <v>2.6244</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.7567</v>
+        <v>2.6244</v>
       </c>
       <c r="N6" t="n">
         <v>138</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.7512</v>
+        <v>2.4197</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4663</v>
+        <v>0.4101</v>
       </c>
       <c r="D7" t="n">
-        <v>0.604</v>
+        <v>0.4773</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7512</v>
+        <v>2.4197</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0756</v>
+        <v>2.7608</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3244</v>
+        <v>-0.3411</v>
       </c>
       <c r="H7" t="n">
-        <v>3.3938</v>
+        <v>3.3177</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3938</v>
+        <v>3.3177</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3244</v>
+        <v>-0.3411</v>
       </c>
       <c r="K7" t="n">
         <v>128</v>
@@ -759,7 +759,7 @@
         <v>79</v>
       </c>
       <c r="M7" t="n">
-        <v>3.0694</v>
+        <v>2.9766</v>
       </c>
       <c r="N7" t="n">
         <v>207</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.5617</v>
+        <v>2.3381</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4342</v>
+        <v>0.3963</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5185</v>
+        <v>0.4401</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5617</v>
+        <v>2.3381</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5617</v>
+        <v>2.3381</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.5617</v>
+        <v>2.3925</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5617</v>
+        <v>2.3925</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5617</v>
+        <v>2.3925</v>
       </c>
       <c r="N8" t="n">
         <v>138</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.2831</v>
+        <v>2.284</v>
       </c>
       <c r="C9" t="n">
-        <v>0.387</v>
+        <v>0.3871</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3927</v>
+        <v>0.4155</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2831</v>
+        <v>2.284</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6474</v>
+        <v>1.6566</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6357</v>
+        <v>0.6274</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6474</v>
+        <v>1.6566</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6474</v>
+        <v>1.6566</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6357</v>
+        <v>0.6274</v>
       </c>
       <c r="K9" t="n">
         <v>128</v>
@@ -851,7 +851,7 @@
         <v>79</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2831</v>
+        <v>2.284</v>
       </c>
       <c r="N9" t="n">
         <v>207</v>
@@ -860,93 +860,93 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>facecrack</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.2256</v>
+        <v>2.1532</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3772</v>
+        <v>0.3649</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3667</v>
+        <v>0.356</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2256</v>
+        <v>2.1532</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2256</v>
+        <v>1.7463</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.4069</v>
       </c>
       <c r="H10" t="n">
-        <v>2.2256</v>
+        <v>1.7463</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2256</v>
+        <v>1.7463</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.4069</v>
       </c>
       <c r="K10" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M10" t="n">
-        <v>2.2256</v>
+        <v>2.1532</v>
       </c>
       <c r="N10" t="n">
-        <v>133</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>facecrack</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1311</v>
+        <v>2.1281</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3612</v>
+        <v>0.3607</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3241</v>
+        <v>0.3446</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1311</v>
+        <v>2.1281</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7213</v>
+        <v>2.1281</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4098</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.7213</v>
+        <v>2.1281</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7213</v>
+        <v>2.1281</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4098</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="L11" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.1311</v>
+        <v>2.1281</v>
       </c>
       <c r="N11" t="n">
-        <v>207</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.0208</v>
+        <v>2.1157</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3425</v>
+        <v>0.3586</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2743</v>
+        <v>0.3389</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0208</v>
+        <v>2.1157</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6476</v>
+        <v>1.7575</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3732</v>
+        <v>0.3582</v>
       </c>
       <c r="H12" t="n">
-        <v>1.6476</v>
+        <v>1.7575</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6476</v>
+        <v>1.7575</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3732</v>
+        <v>0.3582</v>
       </c>
       <c r="K12" t="n">
         <v>128</v>
@@ -989,7 +989,7 @@
         <v>79</v>
       </c>
       <c r="M12" t="n">
-        <v>2.0208</v>
+        <v>2.1157</v>
       </c>
       <c r="N12" t="n">
         <v>207</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.138</v>
+        <v>1.0936</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1929</v>
+        <v>0.1854</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1243</v>
+        <v>-0.1264</v>
       </c>
       <c r="E13" t="n">
-        <v>1.138</v>
+        <v>1.0936</v>
       </c>
       <c r="F13" t="n">
-        <v>1.138</v>
+        <v>1.0936</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.138</v>
+        <v>1.0936</v>
       </c>
       <c r="I13" t="n">
-        <v>1.138</v>
+        <v>1.0936</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.138</v>
+        <v>1.0936</v>
       </c>
       <c r="N13" t="n">
         <v>137</v>
@@ -1044,93 +1044,93 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9154</v>
+        <v>0.8542</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1551</v>
+        <v>0.1448</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2248</v>
+        <v>-0.2354</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9154</v>
+        <v>0.8542</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9154</v>
+        <v>1.3361</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.4819</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9154</v>
+        <v>1.3361</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9154</v>
+        <v>1.3361</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.4819</v>
       </c>
       <c r="K14" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9154</v>
+        <v>0.8542000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>134</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8693</v>
+        <v>0.8515</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1473</v>
+        <v>0.1443</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2456</v>
+        <v>-0.2366</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8693</v>
+        <v>0.8515</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3899</v>
+        <v>0.8515</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5206</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3899</v>
+        <v>0.8515</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3899</v>
+        <v>0.8515</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5206</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="L15" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8693</v>
+        <v>0.8515</v>
       </c>
       <c r="N15" t="n">
-        <v>219</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.7255</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1289</v>
+        <v>0.123</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2946</v>
+        <v>-0.2939</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.7255</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.7255</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.7255</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.7255</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.7255</v>
       </c>
       <c r="N16" t="n">
         <v>137</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.4366</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0857</v>
+        <v>0.074</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4098</v>
+        <v>-0.4255</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.4366</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.4366</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.4366</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.4366</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.4366</v>
       </c>
       <c r="N17" t="n">
         <v>133</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1478</v>
+        <v>0.0896</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0251</v>
+        <v>0.0152</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5713</v>
+        <v>-0.5834</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1478</v>
+        <v>0.0896</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1478</v>
+        <v>0.0896</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1478</v>
+        <v>0.0896</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1478</v>
+        <v>0.0896</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1478</v>
+        <v>0.0896</v>
       </c>
       <c r="N18" t="n">
         <v>133</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0571</v>
+        <v>0.0097</v>
       </c>
       <c r="C19" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.6198</v>
+      </c>
+      <c r="E19" t="n">
         <v>0.0097</v>
       </c>
-      <c r="D19" t="n">
-        <v>-0.6122</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.0571</v>
-      </c>
       <c r="F19" t="n">
-        <v>0.0571</v>
+        <v>0.0097</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0571</v>
+        <v>0.0097</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0571</v>
+        <v>0.0097</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0571</v>
+        <v>0.0097</v>
       </c>
       <c r="N19" t="n">
         <v>134</v>
@@ -1320,139 +1320,139 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>SANJI</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.2666</v>
+        <v>-0.1811</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0452</v>
+        <v>-0.0307</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7584</v>
+        <v>-0.7066</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2666</v>
+        <v>-0.1811</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2666</v>
+        <v>-1.1715</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2666</v>
+        <v>-1.1715</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2666</v>
+        <v>-1.1715</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2666</v>
+        <v>-0.1811</v>
       </c>
       <c r="N20" t="n">
-        <v>138</v>
+        <v>219</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.2936</v>
+        <v>-0.2784</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0498</v>
+        <v>-0.0472</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7706</v>
+        <v>-0.7509</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2936</v>
+        <v>-0.2784</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2936</v>
+        <v>-0.2784</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2936</v>
+        <v>-0.2784</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2936</v>
+        <v>-0.2784</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2936</v>
+        <v>-0.2784</v>
       </c>
       <c r="N21" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SANJI</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.3277</v>
+        <v>-0.3902</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0555</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.786</v>
+        <v>-0.8018</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3277</v>
+        <v>-0.3902</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.243</v>
+        <v>-0.3902</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9153</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.243</v>
+        <v>-0.3902</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.243</v>
+        <v>-0.3902</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9153</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="L22" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3277000000000001</v>
+        <v>-0.3902</v>
       </c>
       <c r="N22" t="n">
-        <v>219</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5434</v>
+        <v>-0.6109</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0921</v>
+        <v>-0.1035</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8833</v>
+        <v>-0.9023</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5434</v>
+        <v>-0.6109</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5434</v>
+        <v>-0.6109</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5434</v>
+        <v>-0.6109</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5434</v>
+        <v>-0.6109</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5434</v>
+        <v>-0.6109</v>
       </c>
       <c r="N23" t="n">
         <v>134</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.648</v>
+        <v>-0.6407</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1098</v>
+        <v>-0.1086</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.9306</v>
+        <v>-0.9159</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.648</v>
+        <v>-0.6407</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.648</v>
+        <v>-0.6407</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.648</v>
+        <v>-0.6407</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.648</v>
+        <v>-0.6407</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.648</v>
+        <v>-0.6407</v>
       </c>
       <c r="N24" t="n">
         <v>137</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.6573</v>
+        <v>-0.7091</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1114</v>
+        <v>-0.1202</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.9348</v>
+        <v>-0.947</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.6573</v>
+        <v>-0.7091</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6573</v>
+        <v>-0.7091</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.6573</v>
+        <v>-0.7091</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.6573</v>
+        <v>-0.7091</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.6573</v>
+        <v>-0.7091</v>
       </c>
       <c r="N25" t="n">
         <v>134</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.6937</v>
+        <v>-0.7171999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1176</v>
+        <v>-0.1216</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.9512</v>
+        <v>-0.9507</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.6937</v>
+        <v>-0.7171999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6937</v>
+        <v>-0.7171999999999999</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.6937</v>
+        <v>-0.7171999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6937</v>
+        <v>-0.7171999999999999</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.6937</v>
+        <v>-0.7171999999999999</v>
       </c>
       <c r="N26" t="n">
         <v>138</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.8414</v>
+        <v>-0.7877999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1426</v>
+        <v>-0.1335</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.0179</v>
+        <v>-0.9828</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.8414</v>
+        <v>-0.7877999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1586</v>
+        <v>0.2122</v>
       </c>
       <c r="G27" t="n">
         <v>-1</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1586</v>
+        <v>0.2122</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1586</v>
+        <v>0.2122</v>
       </c>
       <c r="J27" t="n">
         <v>-1</v>
@@ -1679,7 +1679,7 @@
         <v>79</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.8414</v>
+        <v>-0.7878000000000001</v>
       </c>
       <c r="N27" t="n">
         <v>219</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.8502</v>
+        <v>-0.9202</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1441</v>
+        <v>-0.156</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.0218</v>
+        <v>-1.0431</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.8502</v>
+        <v>-0.9202</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.8502</v>
+        <v>-0.9202</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.8502</v>
+        <v>-0.9202</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.8502</v>
+        <v>-0.9202</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.8502</v>
+        <v>-0.9202</v>
       </c>
       <c r="N28" t="n">
         <v>134</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.1697</v>
+        <v>-1.1669</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1982</v>
+        <v>-0.1978</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.1661</v>
+        <v>-1.1554</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.1697</v>
+        <v>-1.1669</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.1697</v>
+        <v>-1.1669</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.1697</v>
+        <v>-1.1669</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.1697</v>
+        <v>-1.1669</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.1697</v>
+        <v>-1.1669</v>
       </c>
       <c r="N29" t="n">
         <v>137</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.462</v>
+        <v>-1.4233</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2478</v>
+        <v>-0.2412</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.298</v>
+        <v>-1.2721</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.462</v>
+        <v>-1.4233</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.462</v>
+        <v>-1.4233</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.462</v>
+        <v>-1.4233</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.462</v>
+        <v>-1.4233</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.462</v>
+        <v>-1.4233</v>
       </c>
       <c r="N30" t="n">
         <v>138</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.6671</v>
+        <v>-1.621</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2826</v>
+        <v>-0.2747</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.3906</v>
+        <v>-1.3621</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.6671</v>
+        <v>-1.621</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.6671</v>
+        <v>-1.621</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.6671</v>
+        <v>-1.621</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.6671</v>
+        <v>-1.621</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.6671</v>
+        <v>-1.621</v>
       </c>
       <c r="N31" t="n">
         <v>133</v>
@@ -1969,10 +1969,10 @@
         <v>1.3</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5727</v>
+        <v>0.5648</v>
       </c>
       <c r="J2" t="n">
-        <v>16.6083</v>
+        <v>16.3792</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.27</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5226</v>
+        <v>0.5189</v>
       </c>
       <c r="J3" t="n">
-        <v>15.1554</v>
+        <v>15.0481</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>1.11</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2421</v>
+        <v>0.2543</v>
       </c>
       <c r="J4" t="n">
-        <v>7.0209</v>
+        <v>7.3747</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>1.09</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2027</v>
+        <v>0.2162</v>
       </c>
       <c r="J5" t="n">
-        <v>5.8783</v>
+        <v>6.2698</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.95</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.6332</v>
+        <v>-2.8304</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.51</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2431</v>
+        <v>1.2649</v>
       </c>
       <c r="J7" t="n">
-        <v>36.0499</v>
+        <v>36.6821</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>0.92</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2763</v>
+        <v>-0.2782</v>
       </c>
       <c r="J8" t="n">
-        <v>-8.012700000000001</v>
+        <v>-8.0678</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5789</v>
+        <v>-0.553</v>
       </c>
       <c r="J9" t="n">
-        <v>-16.7881</v>
+        <v>-16.037</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5789</v>
+        <v>-0.553</v>
       </c>
       <c r="J10" t="n">
-        <v>-16.7881</v>
+        <v>-16.037</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8827</v>
+        <v>-0.8194</v>
       </c>
       <c r="J11" t="n">
-        <v>-25.5983</v>
+        <v>-23.7626</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.4</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5321</v>
+        <v>0.536</v>
       </c>
       <c r="J12" t="n">
-        <v>14.8988</v>
+        <v>15.008</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.32</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4386</v>
+        <v>0.4477</v>
       </c>
       <c r="J13" t="n">
-        <v>12.2808</v>
+        <v>12.5356</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>1.15</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2283</v>
+        <v>0.2441</v>
       </c>
       <c r="J14" t="n">
-        <v>6.3924</v>
+        <v>6.8348</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>0.88</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1678</v>
+        <v>-0.1784</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.6984</v>
+        <v>-4.9952</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.78</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2705</v>
+        <v>-0.2811</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.574</v>
+        <v>-7.8708</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.07</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1497</v>
+        <v>0.1569</v>
       </c>
       <c r="J17" t="n">
-        <v>4.1916</v>
+        <v>4.3932</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>0.99</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0168</v>
+        <v>-0.0224</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4704</v>
+        <v>-0.6272</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>0.95</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0718</v>
+        <v>-0.0829</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.0104</v>
+        <v>-2.3212</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.88</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1507</v>
+        <v>-0.1651</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.2196</v>
+        <v>-4.6228</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.87</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1614</v>
+        <v>-0.1759</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.5192</v>
+        <v>-4.9252</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.4</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8332000000000001</v>
+        <v>0.7849</v>
       </c>
       <c r="J22" t="n">
-        <v>18.3304</v>
+        <v>17.2678</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.13</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3355</v>
+        <v>0.331</v>
       </c>
       <c r="J23" t="n">
-        <v>7.381</v>
+        <v>7.282</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>0.95</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.4982</v>
+        <v>-1.7644</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>0.7</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3255</v>
+        <v>-0.3392</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.161</v>
+        <v>-7.4624</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.37</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6266</v>
+        <v>-0.6248</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.7852</v>
+        <v>-13.7456</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>1.82</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5098</v>
+        <v>1.6388</v>
       </c>
       <c r="J27" t="n">
-        <v>33.2156</v>
+        <v>36.0536</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>1.68</v>
       </c>
       <c r="I28" t="n">
-        <v>1.3423</v>
+        <v>1.4337</v>
       </c>
       <c r="J28" t="n">
-        <v>29.5306</v>
+        <v>31.5414</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>1.12</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3366</v>
+        <v>0.3465</v>
       </c>
       <c r="J29" t="n">
-        <v>7.4052</v>
+        <v>7.623</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>1.05</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1301</v>
+        <v>0.154</v>
       </c>
       <c r="J30" t="n">
-        <v>2.8622</v>
+        <v>3.388</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.79</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.6627</v>
       </c>
       <c r="J31" t="n">
-        <v>-15.8686</v>
+        <v>-14.5794</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.05</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1989</v>
+        <v>0.1914</v>
       </c>
       <c r="J32" t="n">
-        <v>5.7681</v>
+        <v>5.5506</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.02</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1204</v>
+        <v>0.1129</v>
       </c>
       <c r="J33" t="n">
-        <v>3.4916</v>
+        <v>3.2741</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>0.8</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2169</v>
+        <v>-0.2353</v>
       </c>
       <c r="J34" t="n">
-        <v>-6.2901</v>
+        <v>-6.8237</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3223</v>
+        <v>-0.3385</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.3467</v>
+        <v>-9.8165</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.52</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4811</v>
+        <v>-0.4899</v>
       </c>
       <c r="J36" t="n">
-        <v>-13.9519</v>
+        <v>-14.2071</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.42</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0364</v>
+        <v>0.9842</v>
       </c>
       <c r="J37" t="n">
-        <v>30.0556</v>
+        <v>28.5418</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.41</v>
       </c>
       <c r="I38" t="n">
-        <v>1.0214</v>
+        <v>0.9668</v>
       </c>
       <c r="J38" t="n">
-        <v>29.6206</v>
+        <v>28.0372</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.29</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7705</v>
+        <v>0.7327</v>
       </c>
       <c r="J39" t="n">
-        <v>22.3445</v>
+        <v>21.2483</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>1.06</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1841</v>
+        <v>0.1997</v>
       </c>
       <c r="J40" t="n">
-        <v>5.3389</v>
+        <v>5.7913</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.82</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6231</v>
+        <v>-0.579</v>
       </c>
       <c r="J41" t="n">
-        <v>-18.0699</v>
+        <v>-16.791</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>0.95</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.0442</v>
+        <v>-0.0616</v>
       </c>
       <c r="J42" t="n">
-        <v>-1.105</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>0.91</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.0944</v>
+        <v>-0.1134</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.36</v>
+        <v>-2.835</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3163</v>
+        <v>-0.3338</v>
       </c>
       <c r="J44" t="n">
-        <v>-7.9075</v>
+        <v>-8.345000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>0.68</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3257</v>
+        <v>-0.3429</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.1425</v>
+        <v>-8.5725</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>0.64</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3634</v>
+        <v>-0.3791</v>
       </c>
       <c r="J46" t="n">
-        <v>-9.085000000000001</v>
+        <v>-9.477499999999999</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>2.14</v>
       </c>
       <c r="I47" t="n">
-        <v>1.8338</v>
+        <v>1.8855</v>
       </c>
       <c r="J47" t="n">
-        <v>45.845</v>
+        <v>47.1375</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.24</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6383</v>
+        <v>0.6189</v>
       </c>
       <c r="J48" t="n">
-        <v>15.9575</v>
+        <v>15.4725</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>1.24</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6383</v>
+        <v>0.6189</v>
       </c>
       <c r="J49" t="n">
-        <v>15.9575</v>
+        <v>15.4725</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.96</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2402</v>
+        <v>-0.2216</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.005</v>
+        <v>-5.54</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.9</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4262</v>
+        <v>-0.3961</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.655</v>
+        <v>-9.9025</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.33</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6773</v>
+        <v>0.6505</v>
       </c>
       <c r="J52" t="n">
-        <v>16.9325</v>
+        <v>16.2625</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.08</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2098</v>
+        <v>0.2159</v>
       </c>
       <c r="J53" t="n">
-        <v>5.245</v>
+        <v>5.3975</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0025</v>
+        <v>0.0018</v>
       </c>
       <c r="J54" t="n">
-        <v>0.0625</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>0.78</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2566</v>
+        <v>-0.2702</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.415</v>
+        <v>-6.755</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.71</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3245</v>
+        <v>-0.3366</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.112500000000001</v>
+        <v>-8.414999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9113</v>
+        <v>0.8517</v>
       </c>
       <c r="J57" t="n">
-        <v>22.7825</v>
+        <v>21.2925</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>1.13</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3986</v>
+        <v>0.3952</v>
       </c>
       <c r="J58" t="n">
-        <v>9.965</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>1.11</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3465</v>
+        <v>0.347</v>
       </c>
       <c r="J59" t="n">
-        <v>8.6625</v>
+        <v>8.675000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>1.1</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3193</v>
+        <v>0.3217</v>
       </c>
       <c r="J60" t="n">
-        <v>7.9825</v>
+        <v>8.0425</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2629</v>
+        <v>-0.2539</v>
       </c>
       <c r="J61" t="n">
-        <v>-6.5725</v>
+        <v>-6.3475</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>0.89</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.1139</v>
+        <v>-0.1341</v>
       </c>
       <c r="J62" t="n">
-        <v>-2.7336</v>
+        <v>-3.2184</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>0.82</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.1902</v>
+        <v>-0.2103</v>
       </c>
       <c r="J63" t="n">
-        <v>-4.5648</v>
+        <v>-5.0472</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>0.79</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2204</v>
+        <v>-0.2402</v>
       </c>
       <c r="J64" t="n">
-        <v>-5.2896</v>
+        <v>-5.7648</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.71</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2949</v>
+        <v>-0.3136</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.0776</v>
+        <v>-7.5264</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.57</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4262</v>
+        <v>-0.4394</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.2288</v>
+        <v>-10.5456</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.69</v>
       </c>
       <c r="I67" t="n">
-        <v>1.3555</v>
+        <v>1.3364</v>
       </c>
       <c r="J67" t="n">
-        <v>32.532</v>
+        <v>32.0736</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.57</v>
       </c>
       <c r="I68" t="n">
-        <v>1.2092</v>
+        <v>1.1806</v>
       </c>
       <c r="J68" t="n">
-        <v>29.0208</v>
+        <v>28.3344</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>1.28</v>
       </c>
       <c r="I69" t="n">
-        <v>0.7309</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="J69" t="n">
-        <v>17.5416</v>
+        <v>16.8264</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>1.26</v>
       </c>
       <c r="I70" t="n">
-        <v>0.6861</v>
+        <v>0.6611</v>
       </c>
       <c r="J70" t="n">
-        <v>16.4664</v>
+        <v>15.8664</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.64</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.0849</v>
+        <v>-0.9815</v>
       </c>
       <c r="J71" t="n">
-        <v>-26.0376</v>
+        <v>-23.556</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.12</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4469</v>
+        <v>0.4093</v>
       </c>
       <c r="J72" t="n">
-        <v>11.1725</v>
+        <v>10.2325</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>0.78</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.2169</v>
+        <v>-0.2397</v>
       </c>
       <c r="J73" t="n">
-        <v>-5.4225</v>
+        <v>-5.9925</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>0.62</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.3677</v>
+        <v>-0.3858</v>
       </c>
       <c r="J74" t="n">
-        <v>-9.192500000000001</v>
+        <v>-9.645</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>0.46</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.5173</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="J75" t="n">
-        <v>-12.9325</v>
+        <v>-13.1675</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>0.43</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5454</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="J76" t="n">
-        <v>-13.635</v>
+        <v>-13.8225</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>2.22</v>
       </c>
       <c r="I77" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J77" t="n">
-        <v>45.845</v>
+        <v>48.43</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>1.39</v>
       </c>
       <c r="I78" t="n">
-        <v>0.9552</v>
+        <v>0.904</v>
       </c>
       <c r="J78" t="n">
-        <v>23.88</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>1.13</v>
       </c>
       <c r="I79" t="n">
-        <v>0.352</v>
+        <v>0.3631</v>
       </c>
       <c r="J79" t="n">
-        <v>8.800000000000001</v>
+        <v>9.077500000000001</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>1.04</v>
       </c>
       <c r="I80" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.1139</v>
       </c>
       <c r="J80" t="n">
-        <v>2.125</v>
+        <v>2.8475</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3164</v>
+        <v>-0.2915</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.91</v>
+        <v>-7.2875</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.14</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4172</v>
+        <v>0.3953</v>
       </c>
       <c r="J82" t="n">
-        <v>9.595599999999999</v>
+        <v>9.091900000000001</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>0.86</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.1528</v>
+        <v>-0.172</v>
       </c>
       <c r="J83" t="n">
-        <v>-3.5144</v>
+        <v>-3.956</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>0.78</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2328</v>
+        <v>-0.2518</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.3544</v>
+        <v>-5.7914</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>0.7</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3082</v>
+        <v>-0.3258</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.0886</v>
+        <v>-7.4934</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.44</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5505</v>
+        <v>-0.5556</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.6615</v>
+        <v>-12.7788</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.83</v>
       </c>
       <c r="I87" t="n">
-        <v>1.5008</v>
+        <v>1.4932</v>
       </c>
       <c r="J87" t="n">
-        <v>34.5184</v>
+        <v>34.3436</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.56</v>
       </c>
       <c r="I88" t="n">
-        <v>1.1812</v>
+        <v>1.1537</v>
       </c>
       <c r="J88" t="n">
-        <v>27.1676</v>
+        <v>26.5351</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>1.22</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5754</v>
+        <v>0.5658</v>
       </c>
       <c r="J89" t="n">
-        <v>13.2342</v>
+        <v>13.0134</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>1.22</v>
       </c>
       <c r="I90" t="n">
-        <v>0.5754</v>
+        <v>0.5658</v>
       </c>
       <c r="J90" t="n">
-        <v>13.2342</v>
+        <v>13.0134</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>1.02</v>
       </c>
       <c r="I91" t="n">
-        <v>0.0074</v>
+        <v>0.0397</v>
       </c>
       <c r="J91" t="n">
-        <v>0.1702</v>
+        <v>0.9131</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.26</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5622</v>
+        <v>0.5446</v>
       </c>
       <c r="J92" t="n">
-        <v>15.7416</v>
+        <v>15.2488</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>1.03</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1</v>
+        <v>0.1059</v>
       </c>
       <c r="J93" t="n">
-        <v>2.8</v>
+        <v>2.9652</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>0.99</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0176</v>
+        <v>-0.023</v>
       </c>
       <c r="J94" t="n">
-        <v>-0.4928</v>
+        <v>-0.644</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.79</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2442</v>
+        <v>-0.2586</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.8376</v>
+        <v>-7.2408</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.73</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3029</v>
+        <v>-0.3161</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.481199999999999</v>
+        <v>-8.8508</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.36</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9545</v>
+        <v>0.8919</v>
       </c>
       <c r="J97" t="n">
-        <v>26.726</v>
+        <v>24.9732</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.2</v>
       </c>
       <c r="I98" t="n">
-        <v>0.576</v>
+        <v>0.556</v>
       </c>
       <c r="J98" t="n">
-        <v>16.128</v>
+        <v>15.568</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.06</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2025</v>
+        <v>0.2124</v>
       </c>
       <c r="J99" t="n">
-        <v>5.67</v>
+        <v>5.9472</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>1.03</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1035</v>
+        <v>0.1174</v>
       </c>
       <c r="J100" t="n">
-        <v>2.898</v>
+        <v>3.2872</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.97</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1623</v>
+        <v>-0.1578</v>
       </c>
       <c r="J101" t="n">
-        <v>-4.5444</v>
+        <v>-4.4184</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.15</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3528</v>
+        <v>0.3519</v>
       </c>
       <c r="J102" t="n">
-        <v>10.584</v>
+        <v>10.557</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>1.1</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2532</v>
+        <v>0.2575</v>
       </c>
       <c r="J103" t="n">
-        <v>7.596</v>
+        <v>7.725</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>1.05</v>
       </c>
       <c r="I104" t="n">
-        <v>0.145</v>
+        <v>0.152</v>
       </c>
       <c r="J104" t="n">
-        <v>4.35</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>0.95</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.07340000000000001</v>
+        <v>-0.0842</v>
       </c>
       <c r="J105" t="n">
-        <v>-2.202</v>
+        <v>-2.526</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.62</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4081</v>
+        <v>-0.4174</v>
       </c>
       <c r="J106" t="n">
-        <v>-12.243</v>
+        <v>-12.522</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.39</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7201</v>
+        <v>0.6987</v>
       </c>
       <c r="J107" t="n">
-        <v>21.603</v>
+        <v>20.961</v>
       </c>
     </row>
     <row r="108">
@@ -6249,10 +6249,10 @@
         <v>1.2</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4035</v>
+        <v>0.4081</v>
       </c>
       <c r="J109" t="n">
-        <v>12.105</v>
+        <v>12.243</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>0.95</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.0906</v>
+        <v>-0.0975</v>
       </c>
       <c r="J110" t="n">
-        <v>-2.718</v>
+        <v>-2.925</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>0.93</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.115</v>
+        <v>-0.1232</v>
       </c>
       <c r="J111" t="n">
-        <v>-3.45</v>
+        <v>-3.696</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.39</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7561</v>
+        <v>0.7252</v>
       </c>
       <c r="J112" t="n">
-        <v>22.683</v>
+        <v>21.756</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>1.15</v>
       </c>
       <c r="I113" t="n">
-        <v>0.3354</v>
+        <v>0.3392</v>
       </c>
       <c r="J113" t="n">
-        <v>10.062</v>
+        <v>10.176</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>0.92</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1156</v>
+        <v>-0.1266</v>
       </c>
       <c r="J114" t="n">
-        <v>-3.468</v>
+        <v>-3.798</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>0.88</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1602</v>
+        <v>-0.1725</v>
       </c>
       <c r="J115" t="n">
-        <v>-4.806</v>
+        <v>-5.175</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.84</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2025</v>
+        <v>-0.2151</v>
       </c>
       <c r="J116" t="n">
-        <v>-6.075</v>
+        <v>-6.453</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.45</v>
       </c>
       <c r="I117" t="n">
-        <v>0.8499</v>
+        <v>0.8099</v>
       </c>
       <c r="J117" t="n">
-        <v>25.497</v>
+        <v>24.297</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.14</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3136</v>
+        <v>0.3192</v>
       </c>
       <c r="J118" t="n">
-        <v>9.407999999999999</v>
+        <v>9.576000000000001</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>0.99</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0247</v>
+        <v>-0.0284</v>
       </c>
       <c r="J119" t="n">
-        <v>-0.741</v>
+        <v>-0.852</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>0.95</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.0808</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="J120" t="n">
-        <v>-2.424</v>
+        <v>-2.697</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.71</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.332</v>
+        <v>-0.3426</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.960000000000001</v>
+        <v>-10.278</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.32</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6456</v>
+        <v>0.6243</v>
       </c>
       <c r="J122" t="n">
-        <v>19.368</v>
+        <v>18.729</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.19</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4154</v>
+        <v>0.413</v>
       </c>
       <c r="J123" t="n">
-        <v>12.462</v>
+        <v>12.39</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>1.13</v>
       </c>
       <c r="I124" t="n">
-        <v>0.302</v>
+        <v>0.3066</v>
       </c>
       <c r="J124" t="n">
-        <v>9.06</v>
+        <v>9.198</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>0.75</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2901</v>
+        <v>-0.3024</v>
       </c>
       <c r="J125" t="n">
-        <v>-8.702999999999999</v>
+        <v>-9.071999999999999</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3475</v>
+        <v>-0.3582</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.425</v>
+        <v>-10.746</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.4</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7869</v>
+        <v>0.7506</v>
       </c>
       <c r="J127" t="n">
-        <v>23.607</v>
+        <v>22.518</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.03</v>
       </c>
       <c r="I128" t="n">
-        <v>0.0915</v>
+        <v>0.0997</v>
       </c>
       <c r="J128" t="n">
-        <v>2.745</v>
+        <v>2.991</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>0.98</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0361</v>
+        <v>-0.0428</v>
       </c>
       <c r="J129" t="n">
-        <v>-1.083</v>
+        <v>-1.284</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2292</v>
+        <v>-0.2426</v>
       </c>
       <c r="J130" t="n">
-        <v>-6.876</v>
+        <v>-7.278</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.79</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2492</v>
+        <v>-0.2625</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.476</v>
+        <v>-7.875</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.43</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0805</v>
+        <v>1.0304</v>
       </c>
       <c r="J132" t="n">
-        <v>32.415</v>
+        <v>30.912</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.22</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6377</v>
+        <v>0.6086</v>
       </c>
       <c r="J133" t="n">
-        <v>19.131</v>
+        <v>18.258</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>0.98</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.115</v>
+        <v>-0.1142</v>
       </c>
       <c r="J134" t="n">
-        <v>-3.45</v>
+        <v>-3.426</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>0.95</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2204</v>
+        <v>-0.2163</v>
       </c>
       <c r="J135" t="n">
-        <v>-6.612</v>
+        <v>-6.489</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.85</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5134</v>
+        <v>-0.4863</v>
       </c>
       <c r="J136" t="n">
-        <v>-15.402</v>
+        <v>-14.589</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.36</v>
       </c>
       <c r="I137" t="n">
-        <v>0.7316</v>
+        <v>0.699</v>
       </c>
       <c r="J137" t="n">
-        <v>21.948</v>
+        <v>20.97</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>1.2</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4474</v>
+        <v>0.4401</v>
       </c>
       <c r="J138" t="n">
-        <v>13.422</v>
+        <v>13.203</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>0.92</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1089</v>
+        <v>-0.1215</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.267</v>
+        <v>-3.645</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.76</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2755</v>
+        <v>-0.289</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.265000000000001</v>
+        <v>-8.67</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.63</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3989</v>
+        <v>-0.4086</v>
       </c>
       <c r="J141" t="n">
-        <v>-11.967</v>
+        <v>-12.258</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.13</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3113</v>
+        <v>0.3133</v>
       </c>
       <c r="J142" t="n">
-        <v>9.339</v>
+        <v>9.398999999999999</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.04</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1197</v>
+        <v>0.1272</v>
       </c>
       <c r="J143" t="n">
-        <v>3.591</v>
+        <v>3.816</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>0.95</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0742</v>
+        <v>-0.0847</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.226</v>
+        <v>-2.541</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>0.9</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1323</v>
+        <v>-0.1454</v>
       </c>
       <c r="J145" t="n">
-        <v>-3.969</v>
+        <v>-4.362</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>0.89</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1432</v>
+        <v>-0.1567</v>
       </c>
       <c r="J146" t="n">
-        <v>-4.296</v>
+        <v>-4.701</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>1.54</v>
       </c>
       <c r="I147" t="n">
-        <v>0.9842</v>
+        <v>0.9363</v>
       </c>
       <c r="J147" t="n">
-        <v>29.526</v>
+        <v>28.089</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>1</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.0041</v>
+        <v>-0.0031</v>
       </c>
       <c r="J148" t="n">
-        <v>-0.123</v>
+        <v>-0.093</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>0.96</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.0765</v>
       </c>
       <c r="J149" t="n">
-        <v>-2.055</v>
+        <v>-2.295</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>0.93</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1056</v>
+        <v>-0.1158</v>
       </c>
       <c r="J150" t="n">
-        <v>-3.168</v>
+        <v>-3.474</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.83</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2145</v>
+        <v>-0.2268</v>
       </c>
       <c r="J151" t="n">
-        <v>-6.435</v>
+        <v>-6.804</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.51</v>
       </c>
       <c r="I152" t="n">
-        <v>1.197</v>
+        <v>1.1558</v>
       </c>
       <c r="J152" t="n">
-        <v>33.516</v>
+        <v>32.3624</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>1.06</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2155</v>
+        <v>0.2212</v>
       </c>
       <c r="J153" t="n">
-        <v>6.034</v>
+        <v>6.1936</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>0.99</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0668</v>
+        <v>-0.0679</v>
       </c>
       <c r="J154" t="n">
-        <v>-1.8704</v>
+        <v>-1.9012</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.88</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4226</v>
+        <v>-0.4057</v>
       </c>
       <c r="J155" t="n">
-        <v>-11.8328</v>
+        <v>-11.3596</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.85</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5054999999999999</v>
+        <v>-0.4808</v>
       </c>
       <c r="J156" t="n">
-        <v>-14.154</v>
+        <v>-13.4624</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.4</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7719</v>
+        <v>0.7395</v>
       </c>
       <c r="J157" t="n">
-        <v>21.6132</v>
+        <v>20.706</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.11</v>
       </c>
       <c r="I158" t="n">
-        <v>0.2577</v>
+        <v>0.2654</v>
       </c>
       <c r="J158" t="n">
-        <v>7.2156</v>
+        <v>7.4312</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>1.02</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0615</v>
+        <v>0.0702</v>
       </c>
       <c r="J159" t="n">
-        <v>1.722</v>
+        <v>1.9656</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.0921</v>
+        <v>-0.1021</v>
       </c>
       <c r="J160" t="n">
-        <v>-2.5788</v>
+        <v>-2.8588</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.72</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3214</v>
+        <v>-0.3325</v>
       </c>
       <c r="J161" t="n">
-        <v>-8.9992</v>
+        <v>-9.31</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.24</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5222</v>
+        <v>0.5087</v>
       </c>
       <c r="J162" t="n">
-        <v>14.6216</v>
+        <v>14.2436</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>1</v>
       </c>
       <c r="I163" t="n">
-        <v>0.0042</v>
+        <v>0.003</v>
       </c>
       <c r="J163" t="n">
-        <v>0.1176</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>1</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0042</v>
+        <v>0.003</v>
       </c>
       <c r="J164" t="n">
-        <v>0.1176</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>0.82</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2153</v>
+        <v>-0.2296</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.0284</v>
+        <v>-6.4288</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>0.79</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2455</v>
+        <v>-0.2595</v>
       </c>
       <c r="J166" t="n">
-        <v>-6.874</v>
+        <v>-7.266</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.47</v>
       </c>
       <c r="I167" t="n">
-        <v>1.1298</v>
+        <v>1.0865</v>
       </c>
       <c r="J167" t="n">
-        <v>31.6344</v>
+        <v>30.422</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>1.33</v>
       </c>
       <c r="I168" t="n">
-        <v>0.898</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="J168" t="n">
-        <v>25.144</v>
+        <v>23.4696</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>1.08</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2675</v>
+        <v>0.2723</v>
       </c>
       <c r="J169" t="n">
-        <v>7.49</v>
+        <v>7.6244</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>0.9</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3772</v>
+        <v>-0.3617</v>
       </c>
       <c r="J170" t="n">
-        <v>-10.5616</v>
+        <v>-10.1276</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.72</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.8519</v>
+        <v>-0.7855</v>
       </c>
       <c r="J171" t="n">
-        <v>-23.8532</v>
+        <v>-21.994</v>
       </c>
     </row>
     <row r="172">
@@ -8769,10 +8769,10 @@
         <v>0.64</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.3048</v>
+        <v>-0.3337</v>
       </c>
       <c r="J172" t="n">
-        <v>-6.096</v>
+        <v>-6.674</v>
       </c>
     </row>
     <row r="173">
@@ -8809,10 +8809,10 @@
         <v>0.59</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.3578</v>
+        <v>-0.3832</v>
       </c>
       <c r="J173" t="n">
-        <v>-7.156</v>
+        <v>-7.664</v>
       </c>
     </row>
     <row r="174">
@@ -8849,10 +8849,10 @@
         <v>0.55</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3982</v>
+        <v>-0.421</v>
       </c>
       <c r="J174" t="n">
-        <v>-7.964</v>
+        <v>-8.42</v>
       </c>
     </row>
     <row r="175">
@@ -8889,10 +8889,10 @@
         <v>0.39</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.5471</v>
+        <v>-0.5595</v>
       </c>
       <c r="J175" t="n">
-        <v>-10.942</v>
+        <v>-11.19</v>
       </c>
     </row>
     <row r="176">
@@ -8929,10 +8929,10 @@
         <v>0.29</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6468</v>
+        <v>-0.6504</v>
       </c>
       <c r="J176" t="n">
-        <v>-12.936</v>
+        <v>-13.008</v>
       </c>
     </row>
     <row r="177">
@@ -8969,10 +8969,10 @@
         <v>2.16</v>
       </c>
       <c r="I177" t="n">
-        <v>1.8075</v>
+        <v>1.8236</v>
       </c>
       <c r="J177" t="n">
-        <v>36.15</v>
+        <v>36.472</v>
       </c>
     </row>
     <row r="178">
@@ -9009,10 +9009,10 @@
         <v>1.69</v>
       </c>
       <c r="I178" t="n">
-        <v>1.2968</v>
+        <v>1.2849</v>
       </c>
       <c r="J178" t="n">
-        <v>25.936</v>
+        <v>25.698</v>
       </c>
     </row>
     <row r="179">
@@ -9049,10 +9049,10 @@
         <v>1.58</v>
       </c>
       <c r="I179" t="n">
-        <v>1.1753</v>
+        <v>1.1537</v>
       </c>
       <c r="J179" t="n">
-        <v>23.506</v>
+        <v>23.074</v>
       </c>
     </row>
     <row r="180">
@@ -9089,10 +9089,10 @@
         <v>1.57</v>
       </c>
       <c r="I180" t="n">
-        <v>1.1639</v>
+        <v>1.1413</v>
       </c>
       <c r="J180" t="n">
-        <v>23.278</v>
+        <v>22.826</v>
       </c>
     </row>
     <row r="181">
@@ -9129,10 +9129,10 @@
         <v>1.19</v>
       </c>
       <c r="I181" t="n">
-        <v>0.4479</v>
+        <v>0.4622</v>
       </c>
       <c r="J181" t="n">
-        <v>8.958</v>
+        <v>9.244</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4686/event_4686_evp_summary.xlsx
+++ b/database/event/4686/event_4686_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.0716</v>
+        <v>6.0108</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0291</v>
+        <v>1.0188</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1397</v>
+        <v>2.1324</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0716</v>
+        <v>6.0108</v>
       </c>
       <c r="F2" t="n">
-        <v>3.011</v>
+        <v>2.8964</v>
       </c>
       <c r="G2" t="n">
-        <v>3.0606</v>
+        <v>3.1144</v>
       </c>
       <c r="H2" t="n">
-        <v>3.8653</v>
+        <v>3.6875</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8653</v>
+        <v>3.6875</v>
       </c>
       <c r="J2" t="n">
-        <v>3.0606</v>
+        <v>3.1144</v>
       </c>
       <c r="K2" t="n">
         <v>140</v>
@@ -529,7 +529,7 @@
         <v>79</v>
       </c>
       <c r="M2" t="n">
-        <v>6.9259</v>
+        <v>6.8019</v>
       </c>
       <c r="N2" t="n">
         <v>219</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.6549</v>
+        <v>3.5193</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.5965</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0396</v>
+        <v>0.9974</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6549</v>
+        <v>3.5193</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4097</v>
+        <v>2.4146</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2452</v>
+        <v>1.1047</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5492</v>
+        <v>2.5833</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5492</v>
+        <v>2.5833</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2452</v>
+        <v>1.1047</v>
       </c>
       <c r="K3" t="n">
         <v>128</v>
@@ -575,7 +575,7 @@
         <v>79</v>
       </c>
       <c r="M3" t="n">
-        <v>3.7944</v>
+        <v>3.688</v>
       </c>
       <c r="N3" t="n">
         <v>207</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.6925</v>
+        <v>2.6532</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4563</v>
+        <v>0.4497</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6015</v>
+        <v>0.6029</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6925</v>
+        <v>2.6532</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9214</v>
+        <v>2.868</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2289</v>
+        <v>-0.2148</v>
       </c>
       <c r="H4" t="n">
-        <v>3.669</v>
+        <v>3.6224</v>
       </c>
       <c r="I4" t="n">
-        <v>3.669</v>
+        <v>3.6224</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2289</v>
+        <v>-0.2148</v>
       </c>
       <c r="K4" t="n">
         <v>140</v>
@@ -621,7 +621,7 @@
         <v>79</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4401</v>
+        <v>3.4076</v>
       </c>
       <c r="N4" t="n">
         <v>219</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.6117</v>
+        <v>2.6248</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4427</v>
+        <v>0.4449</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5647</v>
+        <v>0.5899</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6117</v>
+        <v>2.6248</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6117</v>
+        <v>2.6248</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2.9912</v>
+        <v>3.0651</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9912</v>
+        <v>3.0651</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9912</v>
+        <v>3.0651</v>
       </c>
       <c r="N5" t="n">
         <v>137</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.4441</v>
+        <v>2.3878</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4142</v>
+        <v>0.4047</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4884</v>
+        <v>0.482</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4441</v>
+        <v>2.3878</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4441</v>
+        <v>2.3878</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6244</v>
+        <v>2.522</v>
       </c>
       <c r="I6" t="n">
-        <v>2.6244</v>
+        <v>2.522</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.6244</v>
+        <v>2.522</v>
       </c>
       <c r="N6" t="n">
         <v>138</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.4197</v>
+        <v>2.288</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4101</v>
+        <v>0.3878</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4773</v>
+        <v>0.4365</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4197</v>
+        <v>2.288</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7608</v>
+        <v>2.6906</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3411</v>
+        <v>-0.4026</v>
       </c>
       <c r="H7" t="n">
-        <v>3.3177</v>
+        <v>3.2159</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3177</v>
+        <v>3.2159</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3411</v>
+        <v>-0.4026</v>
       </c>
       <c r="K7" t="n">
         <v>128</v>
@@ -759,7 +759,7 @@
         <v>79</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9766</v>
+        <v>2.8133</v>
       </c>
       <c r="N7" t="n">
         <v>207</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.3381</v>
+        <v>2.2386</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3963</v>
+        <v>0.3794</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4401</v>
+        <v>0.414</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3381</v>
+        <v>2.2386</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3381</v>
+        <v>2.2386</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3925</v>
+        <v>2.2386</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3925</v>
+        <v>2.2386</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3925</v>
+        <v>2.2386</v>
       </c>
       <c r="N8" t="n">
         <v>138</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.284</v>
+        <v>2.1772</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3871</v>
+        <v>0.369</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4155</v>
+        <v>0.386</v>
       </c>
       <c r="E9" t="n">
-        <v>2.284</v>
+        <v>2.1772</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6566</v>
+        <v>1.662</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6274</v>
+        <v>0.5152</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6566</v>
+        <v>1.662</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6566</v>
+        <v>1.662</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6274</v>
+        <v>0.5152</v>
       </c>
       <c r="K9" t="n">
         <v>128</v>
@@ -851,7 +851,7 @@
         <v>79</v>
       </c>
       <c r="M9" t="n">
-        <v>2.284</v>
+        <v>2.1772</v>
       </c>
       <c r="N9" t="n">
         <v>207</v>
@@ -860,35 +860,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>facecrack</t>
+          <t>almazer</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.1532</v>
+        <v>2.1505</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3649</v>
+        <v>0.3645</v>
       </c>
       <c r="D10" t="n">
-        <v>0.356</v>
+        <v>0.3739</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1532</v>
+        <v>2.1505</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7463</v>
+        <v>1.8338</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4069</v>
+        <v>0.3167</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7463</v>
+        <v>1.8338</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7463</v>
+        <v>1.8338</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4069</v>
+        <v>0.3167</v>
       </c>
       <c r="K10" t="n">
         <v>128</v>
@@ -897,7 +897,7 @@
         <v>79</v>
       </c>
       <c r="M10" t="n">
-        <v>2.1532</v>
+        <v>2.1505</v>
       </c>
       <c r="N10" t="n">
         <v>207</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>facecrack</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1281</v>
+        <v>2.016</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3607</v>
+        <v>0.3417</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3446</v>
+        <v>0.3126</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1281</v>
+        <v>2.016</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1281</v>
+        <v>1.6853</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.3307</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1281</v>
+        <v>1.6853</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1281</v>
+        <v>1.6853</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.3307</v>
       </c>
       <c r="K11" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M11" t="n">
-        <v>2.1281</v>
+        <v>2.016</v>
       </c>
       <c r="N11" t="n">
-        <v>133</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>almazer</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.1157</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3586</v>
+        <v>0.339</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3389</v>
+        <v>0.3053</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1157</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7575</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3582</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7575</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7575</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3582</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="L12" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.1157</v>
+        <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>207</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.0936</v>
+        <v>1.0029</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1854</v>
+        <v>0.17</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1264</v>
+        <v>-0.1489</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0936</v>
+        <v>1.0029</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0936</v>
+        <v>1.0029</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0936</v>
+        <v>1.0029</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0936</v>
+        <v>1.0029</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.0936</v>
+        <v>1.0029</v>
       </c>
       <c r="N13" t="n">
         <v>137</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8542</v>
+        <v>0.8509</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1448</v>
+        <v>0.1442</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2354</v>
+        <v>-0.2182</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8542</v>
+        <v>0.8509</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3361</v>
+        <v>1.3039</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4819</v>
+        <v>-0.453</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3361</v>
+        <v>1.3039</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3361</v>
+        <v>1.3039</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4819</v>
+        <v>-0.453</v>
       </c>
       <c r="K14" t="n">
         <v>140</v>
@@ -1081,7 +1081,7 @@
         <v>79</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8542000000000001</v>
+        <v>0.8509</v>
       </c>
       <c r="N14" t="n">
         <v>219</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8515</v>
+        <v>0.7266</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1443</v>
+        <v>0.1231</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2366</v>
+        <v>-0.2748</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8515</v>
+        <v>0.7266</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8515</v>
+        <v>0.7266</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8515</v>
+        <v>0.7266</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8515</v>
+        <v>0.7266</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8515</v>
+        <v>0.7266</v>
       </c>
       <c r="N15" t="n">
         <v>134</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7255</v>
+        <v>0.6616</v>
       </c>
       <c r="C16" t="n">
-        <v>0.123</v>
+        <v>0.1121</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2939</v>
+        <v>-0.3044</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7255</v>
+        <v>0.6616</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7255</v>
+        <v>0.6616</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7255</v>
+        <v>0.6616</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7255</v>
+        <v>0.6616</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7255</v>
+        <v>0.6616</v>
       </c>
       <c r="N16" t="n">
         <v>137</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.4366</v>
+        <v>0.3191</v>
       </c>
       <c r="C17" t="n">
-        <v>0.074</v>
+        <v>0.0541</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4255</v>
+        <v>-0.4604</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4366</v>
+        <v>0.3191</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4366</v>
+        <v>0.3191</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4366</v>
+        <v>0.3191</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4366</v>
+        <v>0.3191</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4366</v>
+        <v>0.3191</v>
       </c>
       <c r="N17" t="n">
         <v>133</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0896</v>
+        <v>0.1391</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0152</v>
+        <v>0.0236</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5834</v>
+        <v>-0.5424</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0896</v>
+        <v>0.1391</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0896</v>
+        <v>0.1391</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0896</v>
+        <v>0.1391</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0896</v>
+        <v>0.1391</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0896</v>
+        <v>0.1391</v>
       </c>
       <c r="N18" t="n">
         <v>133</v>
@@ -1274,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>SANJI</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0097</v>
+        <v>-0.0244</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0016</v>
+        <v>-0.0041</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6198</v>
+        <v>-0.6169</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0097</v>
+        <v>-0.0244</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0097</v>
+        <v>-1.1075</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1.0831</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0097</v>
+        <v>-1.1075</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0097</v>
+        <v>-1.1075</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1.0831</v>
       </c>
       <c r="K19" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0097</v>
+        <v>-0.02439999999999998</v>
       </c>
       <c r="N19" t="n">
-        <v>134</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SANJI</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1811</v>
+        <v>-0.0629</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0307</v>
+        <v>-0.0107</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7066</v>
+        <v>-0.6344</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1811</v>
+        <v>-0.0629</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1715</v>
+        <v>-0.0629</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9903999999999999</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1715</v>
+        <v>-0.0629</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1715</v>
+        <v>-0.0629</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9903999999999999</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="L20" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1811</v>
+        <v>-0.0629</v>
       </c>
       <c r="N20" t="n">
-        <v>219</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.2784</v>
+        <v>-0.3343</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0472</v>
+        <v>-0.0567</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7509</v>
+        <v>-0.7581</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2784</v>
+        <v>-0.3343</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2784</v>
+        <v>-0.3343</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2784</v>
+        <v>-0.3343</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2784</v>
+        <v>-0.3343</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2784</v>
+        <v>-0.3343</v>
       </c>
       <c r="N21" t="n">
         <v>138</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.3902</v>
+        <v>-0.3549</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.0602</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8018</v>
+        <v>-0.7675</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3902</v>
+        <v>-0.3549</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3902</v>
+        <v>-0.3549</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3902</v>
+        <v>-0.3549</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3902</v>
+        <v>-0.3549</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3902</v>
+        <v>-0.3549</v>
       </c>
       <c r="N22" t="n">
         <v>133</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.6109</v>
+        <v>-0.5994</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.1035</v>
+        <v>-0.1016</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9023</v>
+        <v>-0.8788</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6109</v>
+        <v>-0.5994</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6109</v>
+        <v>-0.5994</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6109</v>
+        <v>-0.5994</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6109</v>
+        <v>-0.5994</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6109</v>
+        <v>-0.5994</v>
       </c>
       <c r="N23" t="n">
         <v>134</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.6407</v>
+        <v>-0.6122</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1086</v>
+        <v>-0.1038</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.9159</v>
+        <v>-0.8847</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6407</v>
+        <v>-0.6122</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6407</v>
+        <v>-0.6122</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6407</v>
+        <v>-0.6122</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.6407</v>
+        <v>-0.6122</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.6407</v>
+        <v>-0.6122</v>
       </c>
       <c r="N24" t="n">
         <v>137</v>
@@ -1550,185 +1550,185 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.7091</v>
+        <v>-0.6632</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1202</v>
+        <v>-0.1124</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.947</v>
+        <v>-0.9079</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.7091</v>
+        <v>-0.6632</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.7091</v>
+        <v>-0.6632</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.7091</v>
+        <v>-0.6632</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.7091</v>
+        <v>-0.6632</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.7091</v>
+        <v>-0.6632</v>
       </c>
       <c r="N25" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-0.7502</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1216</v>
+        <v>-0.1271</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.9507</v>
+        <v>-0.9475</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-0.7502</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-0.7502</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-0.7502</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-0.7502</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-0.7502</v>
       </c>
       <c r="N26" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Qikert</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.8446</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1335</v>
+        <v>-0.1431</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.9828</v>
+        <v>-0.9905</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.8446</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2122</v>
+        <v>-0.8446</v>
       </c>
       <c r="G27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2122</v>
+        <v>-0.8446</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2122</v>
+        <v>-0.8446</v>
       </c>
       <c r="J27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="L27" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.7878000000000001</v>
+        <v>-0.8446</v>
       </c>
       <c r="N27" t="n">
-        <v>219</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>Qikert</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.9202</v>
+        <v>-0.863</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.156</v>
+        <v>-0.1463</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.0431</v>
+        <v>-0.9989</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.9202</v>
+        <v>-0.863</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.9202</v>
+        <v>0.137</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.9202</v>
+        <v>0.137</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.9202</v>
+        <v>0.137</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K28" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.9202</v>
+        <v>-0.863</v>
       </c>
       <c r="N28" t="n">
-        <v>134</v>
+        <v>219</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.1669</v>
+        <v>-1.039</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1978</v>
+        <v>-0.1761</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.1554</v>
+        <v>-1.0791</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.1669</v>
+        <v>-1.039</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.1669</v>
+        <v>-1.039</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.1669</v>
+        <v>-1.039</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.1669</v>
+        <v>-1.039</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.1669</v>
+        <v>-1.039</v>
       </c>
       <c r="N29" t="n">
         <v>137</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.4233</v>
+        <v>-1.3189</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2412</v>
+        <v>-0.2235</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.2721</v>
+        <v>-1.2066</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.4233</v>
+        <v>-1.3189</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.4233</v>
+        <v>-1.3189</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.4233</v>
+        <v>-1.3189</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.4233</v>
+        <v>-1.3189</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.4233</v>
+        <v>-1.3189</v>
       </c>
       <c r="N30" t="n">
         <v>138</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.621</v>
+        <v>-1.6056</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2747</v>
+        <v>-0.2721</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.3621</v>
+        <v>-1.3372</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.621</v>
+        <v>-1.6056</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.621</v>
+        <v>-1.6056</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.621</v>
+        <v>-1.6056</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.621</v>
+        <v>-1.6056</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.621</v>
+        <v>-1.6056</v>
       </c>
       <c r="N31" t="n">
         <v>133</v>
@@ -1969,10 +1969,10 @@
         <v>1.3</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5648</v>
+        <v>0.5056</v>
       </c>
       <c r="J2" t="n">
-        <v>16.3792</v>
+        <v>14.6624</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.27</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5189</v>
+        <v>0.4605</v>
       </c>
       <c r="J3" t="n">
-        <v>15.0481</v>
+        <v>13.3545</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>1.11</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2543</v>
+        <v>0.212</v>
       </c>
       <c r="J4" t="n">
-        <v>7.3747</v>
+        <v>6.148</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>1.09</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2162</v>
+        <v>0.1778</v>
       </c>
       <c r="J5" t="n">
-        <v>6.2698</v>
+        <v>5.1562</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.95</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.8304</v>
+        <v>-2.3403</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.51</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2649</v>
+        <v>1.3064</v>
       </c>
       <c r="J7" t="n">
-        <v>36.6821</v>
+        <v>37.8856</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>0.92</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2782</v>
+        <v>-0.2406</v>
       </c>
       <c r="J8" t="n">
-        <v>-8.0678</v>
+        <v>-6.9774</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.553</v>
+        <v>-0.5125</v>
       </c>
       <c r="J9" t="n">
-        <v>-16.037</v>
+        <v>-14.8625</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.553</v>
+        <v>-0.5125</v>
       </c>
       <c r="J10" t="n">
-        <v>-16.037</v>
+        <v>-14.8625</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8194</v>
+        <v>-0.7949000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>-23.7626</v>
+        <v>-23.0521</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.4</v>
       </c>
       <c r="I12" t="n">
-        <v>0.536</v>
+        <v>0.4665</v>
       </c>
       <c r="J12" t="n">
-        <v>15.008</v>
+        <v>13.062</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.32</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4477</v>
+        <v>0.3816</v>
       </c>
       <c r="J13" t="n">
-        <v>12.5356</v>
+        <v>10.6848</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>1.15</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2441</v>
+        <v>0.1957</v>
       </c>
       <c r="J14" t="n">
-        <v>6.8348</v>
+        <v>5.4796</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>0.88</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1784</v>
+        <v>-0.158</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.9952</v>
+        <v>-4.424</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.78</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2811</v>
+        <v>-0.263</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.8708</v>
+        <v>-7.364</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.07</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1569</v>
+        <v>0.1396</v>
       </c>
       <c r="J17" t="n">
-        <v>4.3932</v>
+        <v>3.9088</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>0.99</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0224</v>
+        <v>-0.0166</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6272</v>
+        <v>-0.4648</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>0.95</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0829</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.3212</v>
+        <v>-1.918</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.88</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1651</v>
+        <v>-0.1454</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.6228</v>
+        <v>-4.0712</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.87</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1759</v>
+        <v>-0.1559</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.9252</v>
+        <v>-4.3652</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.4</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7849</v>
+        <v>0.7389</v>
       </c>
       <c r="J22" t="n">
-        <v>17.2678</v>
+        <v>16.2558</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.13</v>
       </c>
       <c r="I23" t="n">
-        <v>0.331</v>
+        <v>0.279</v>
       </c>
       <c r="J23" t="n">
-        <v>7.282</v>
+        <v>6.138</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>0.95</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.0669</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.7644</v>
+        <v>-1.4718</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>0.7</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3392</v>
+        <v>-0.3233</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.4624</v>
+        <v>-7.1126</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.37</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6248</v>
+        <v>-0.6452</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.7456</v>
+        <v>-14.1944</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>1.82</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6388</v>
+        <v>1.6684</v>
       </c>
       <c r="J27" t="n">
-        <v>36.0536</v>
+        <v>36.7048</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>1.68</v>
       </c>
       <c r="I28" t="n">
-        <v>1.4337</v>
+        <v>1.4691</v>
       </c>
       <c r="J28" t="n">
-        <v>31.5414</v>
+        <v>32.3202</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>1.12</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3465</v>
+        <v>0.3143</v>
       </c>
       <c r="J29" t="n">
-        <v>7.623</v>
+        <v>6.9146</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>1.05</v>
       </c>
       <c r="I30" t="n">
-        <v>0.154</v>
+        <v>0.128</v>
       </c>
       <c r="J30" t="n">
-        <v>3.388</v>
+        <v>2.816</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.79</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6627</v>
+        <v>-0.6338</v>
       </c>
       <c r="J31" t="n">
-        <v>-14.5794</v>
+        <v>-13.9436</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.05</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1914</v>
+        <v>0.1547</v>
       </c>
       <c r="J32" t="n">
-        <v>5.5506</v>
+        <v>4.4863</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.02</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1129</v>
+        <v>0.0873</v>
       </c>
       <c r="J33" t="n">
-        <v>3.2741</v>
+        <v>2.5317</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>0.8</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2353</v>
+        <v>-0.2173</v>
       </c>
       <c r="J34" t="n">
-        <v>-6.8237</v>
+        <v>-6.3017</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3385</v>
+        <v>-0.3228</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.8165</v>
+        <v>-9.3612</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.52</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4899</v>
+        <v>-0.4879</v>
       </c>
       <c r="J36" t="n">
-        <v>-14.2071</v>
+        <v>-14.1491</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.42</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9842</v>
+        <v>0.9785</v>
       </c>
       <c r="J37" t="n">
-        <v>28.5418</v>
+        <v>28.3765</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.41</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9668</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>28.0372</v>
+        <v>27.7878</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.29</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7327</v>
+        <v>0.7044</v>
       </c>
       <c r="J39" t="n">
-        <v>21.2483</v>
+        <v>20.4276</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>1.06</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1997</v>
+        <v>0.1715</v>
       </c>
       <c r="J40" t="n">
-        <v>5.7913</v>
+        <v>4.9735</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.82</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.579</v>
+        <v>-0.5426</v>
       </c>
       <c r="J41" t="n">
-        <v>-16.791</v>
+        <v>-15.7354</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>0.95</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.0616</v>
+        <v>-0.0494</v>
       </c>
       <c r="J42" t="n">
-        <v>-1.54</v>
+        <v>-1.235</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>0.91</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1134</v>
+        <v>-0.0988</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.835</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3338</v>
+        <v>-0.3184</v>
       </c>
       <c r="J44" t="n">
-        <v>-8.345000000000001</v>
+        <v>-7.96</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>0.68</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3429</v>
+        <v>-0.3279</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.5725</v>
+        <v>-8.1975</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>0.64</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3791</v>
+        <v>-0.3661</v>
       </c>
       <c r="J46" t="n">
-        <v>-9.477499999999999</v>
+        <v>-9.1525</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>2.14</v>
       </c>
       <c r="I47" t="n">
-        <v>1.8855</v>
+        <v>1.9614</v>
       </c>
       <c r="J47" t="n">
-        <v>47.1375</v>
+        <v>49.035</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.24</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6189</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="J48" t="n">
-        <v>15.4725</v>
+        <v>14.78</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>1.24</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6189</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="J49" t="n">
-        <v>15.4725</v>
+        <v>14.78</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.96</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2216</v>
+        <v>-0.1889</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.54</v>
+        <v>-4.7225</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.9</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3961</v>
+        <v>-0.3576</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.9025</v>
+        <v>-8.94</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.33</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6505</v>
+        <v>0.5933</v>
       </c>
       <c r="J52" t="n">
-        <v>16.2625</v>
+        <v>14.8325</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.08</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2159</v>
+        <v>0.1728</v>
       </c>
       <c r="J53" t="n">
-        <v>5.3975</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0018</v>
+        <v>0.0008</v>
       </c>
       <c r="J54" t="n">
-        <v>0.045</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>0.78</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2702</v>
+        <v>-0.2509</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.755</v>
+        <v>-6.2725</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.71</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3366</v>
+        <v>-0.3209</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.414999999999999</v>
+        <v>-8.022500000000001</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8517</v>
+        <v>0.8294</v>
       </c>
       <c r="J57" t="n">
-        <v>21.2925</v>
+        <v>20.735</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>1.13</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3952</v>
+        <v>0.3574</v>
       </c>
       <c r="J58" t="n">
-        <v>9.880000000000001</v>
+        <v>8.935</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>1.11</v>
       </c>
       <c r="I59" t="n">
-        <v>0.347</v>
+        <v>0.3104</v>
       </c>
       <c r="J59" t="n">
-        <v>8.675000000000001</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>1.1</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3217</v>
+        <v>0.286</v>
       </c>
       <c r="J60" t="n">
-        <v>8.0425</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2539</v>
+        <v>-0.215</v>
       </c>
       <c r="J61" t="n">
-        <v>-6.3475</v>
+        <v>-5.375</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>0.89</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.1341</v>
+        <v>-0.1189</v>
       </c>
       <c r="J62" t="n">
-        <v>-3.2184</v>
+        <v>-2.8536</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>0.82</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.2103</v>
+        <v>-0.1944</v>
       </c>
       <c r="J63" t="n">
-        <v>-5.0472</v>
+        <v>-4.6656</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>0.79</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2402</v>
+        <v>-0.2242</v>
       </c>
       <c r="J64" t="n">
-        <v>-5.7648</v>
+        <v>-5.3808</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.71</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3136</v>
+        <v>-0.2979</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.5264</v>
+        <v>-7.1496</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.57</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4394</v>
+        <v>-0.4313</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.5456</v>
+        <v>-10.3512</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.69</v>
       </c>
       <c r="I67" t="n">
-        <v>1.3364</v>
+        <v>1.3577</v>
       </c>
       <c r="J67" t="n">
-        <v>32.0736</v>
+        <v>32.5848</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.57</v>
       </c>
       <c r="I68" t="n">
-        <v>1.1806</v>
+        <v>1.1948</v>
       </c>
       <c r="J68" t="n">
-        <v>28.3344</v>
+        <v>28.6752</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>1.28</v>
       </c>
       <c r="I69" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="J69" t="n">
-        <v>16.8264</v>
+        <v>16.2216</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>1.26</v>
       </c>
       <c r="I70" t="n">
-        <v>0.6611</v>
+        <v>0.6345</v>
       </c>
       <c r="J70" t="n">
-        <v>15.8664</v>
+        <v>15.228</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.64</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.9815</v>
+        <v>-0.9838</v>
       </c>
       <c r="J71" t="n">
-        <v>-23.556</v>
+        <v>-23.6112</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.12</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4093</v>
+        <v>0.3792</v>
       </c>
       <c r="J72" t="n">
-        <v>10.2325</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>0.78</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.2397</v>
+        <v>-0.2253</v>
       </c>
       <c r="J73" t="n">
-        <v>-5.9925</v>
+        <v>-5.6325</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>0.62</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.3858</v>
+        <v>-0.3745</v>
       </c>
       <c r="J74" t="n">
-        <v>-9.645</v>
+        <v>-9.362500000000001</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>0.46</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.5266999999999999</v>
+        <v>-0.5282</v>
       </c>
       <c r="J75" t="n">
-        <v>-13.1675</v>
+        <v>-13.205</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>0.43</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5528999999999999</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="J76" t="n">
-        <v>-13.8225</v>
+        <v>-13.95</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>2.22</v>
       </c>
       <c r="I77" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J77" t="n">
-        <v>48.43</v>
+        <v>49.545</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>1.39</v>
       </c>
       <c r="I78" t="n">
-        <v>0.904</v>
+        <v>0.8931</v>
       </c>
       <c r="J78" t="n">
-        <v>22.6</v>
+        <v>22.3275</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>1.13</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3631</v>
+        <v>0.3311</v>
       </c>
       <c r="J79" t="n">
-        <v>9.077500000000001</v>
+        <v>8.2775</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>1.04</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1139</v>
+        <v>0.0895</v>
       </c>
       <c r="J80" t="n">
-        <v>2.8475</v>
+        <v>2.2375</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2915</v>
+        <v>-0.2565</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.2875</v>
+        <v>-6.4125</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.14</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3953</v>
+        <v>0.3492</v>
       </c>
       <c r="J82" t="n">
-        <v>9.091900000000001</v>
+        <v>8.031599999999999</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>0.86</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.172</v>
+        <v>-0.156</v>
       </c>
       <c r="J83" t="n">
-        <v>-3.956</v>
+        <v>-3.588</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>0.78</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2518</v>
+        <v>-0.2348</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.7914</v>
+        <v>-5.4004</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>0.7</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3258</v>
+        <v>-0.3099</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.4934</v>
+        <v>-7.1277</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.44</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5556</v>
+        <v>-0.5624</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.7788</v>
+        <v>-12.9352</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.83</v>
       </c>
       <c r="I87" t="n">
-        <v>1.4932</v>
+        <v>1.5243</v>
       </c>
       <c r="J87" t="n">
-        <v>34.3436</v>
+        <v>35.0589</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.56</v>
       </c>
       <c r="I88" t="n">
-        <v>1.1537</v>
+        <v>1.1684</v>
       </c>
       <c r="J88" t="n">
-        <v>26.5351</v>
+        <v>26.8732</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>1.22</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5658</v>
+        <v>0.5385</v>
       </c>
       <c r="J89" t="n">
-        <v>13.0134</v>
+        <v>12.3855</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>1.22</v>
       </c>
       <c r="I90" t="n">
-        <v>0.5658</v>
+        <v>0.5385</v>
       </c>
       <c r="J90" t="n">
-        <v>13.0134</v>
+        <v>12.3855</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>1.02</v>
       </c>
       <c r="I91" t="n">
-        <v>0.0397</v>
+        <v>0.0217</v>
       </c>
       <c r="J91" t="n">
-        <v>0.9131</v>
+        <v>0.4991</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.26</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5446</v>
+        <v>0.4864</v>
       </c>
       <c r="J92" t="n">
-        <v>15.2488</v>
+        <v>13.6192</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>1.03</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1059</v>
+        <v>0.0779</v>
       </c>
       <c r="J93" t="n">
-        <v>2.9652</v>
+        <v>2.1812</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>0.99</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.023</v>
+        <v>-0.017</v>
       </c>
       <c r="J94" t="n">
-        <v>-0.644</v>
+        <v>-0.476</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.79</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2586</v>
+        <v>-0.2389</v>
       </c>
       <c r="J95" t="n">
-        <v>-7.2408</v>
+        <v>-6.6892</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.73</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3161</v>
+        <v>-0.299</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.8508</v>
+        <v>-8.372</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.36</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8919</v>
+        <v>0.8731</v>
       </c>
       <c r="J97" t="n">
-        <v>24.9732</v>
+        <v>24.4468</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.2</v>
       </c>
       <c r="I98" t="n">
-        <v>0.556</v>
+        <v>0.5182</v>
       </c>
       <c r="J98" t="n">
-        <v>15.568</v>
+        <v>14.5096</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.06</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2124</v>
+        <v>0.1824</v>
       </c>
       <c r="J99" t="n">
-        <v>5.9472</v>
+        <v>5.1072</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>1.03</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1174</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="J100" t="n">
-        <v>3.2872</v>
+        <v>2.6796</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.97</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1578</v>
+        <v>-0.1263</v>
       </c>
       <c r="J101" t="n">
-        <v>-4.4184</v>
+        <v>-3.5364</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.15</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3519</v>
+        <v>0.2979</v>
       </c>
       <c r="J102" t="n">
-        <v>10.557</v>
+        <v>8.936999999999999</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>1.1</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2575</v>
+        <v>0.2102</v>
       </c>
       <c r="J103" t="n">
-        <v>7.725</v>
+        <v>6.306</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>1.05</v>
       </c>
       <c r="I104" t="n">
-        <v>0.152</v>
+        <v>0.1168</v>
       </c>
       <c r="J104" t="n">
-        <v>4.56</v>
+        <v>3.504</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>0.95</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.0842</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="J105" t="n">
-        <v>-2.526</v>
+        <v>-2.073</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.62</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4174</v>
+        <v>-0.4087</v>
       </c>
       <c r="J106" t="n">
-        <v>-12.522</v>
+        <v>-12.261</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.39</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6987</v>
+        <v>0.64</v>
       </c>
       <c r="J107" t="n">
-        <v>20.961</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.24</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4723</v>
+        <v>0.4152</v>
       </c>
       <c r="J108" t="n">
-        <v>14.169</v>
+        <v>12.456</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>1.2</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4081</v>
+        <v>0.354</v>
       </c>
       <c r="J109" t="n">
-        <v>12.243</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>0.95</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.0975</v>
+        <v>-0.0805</v>
       </c>
       <c r="J110" t="n">
-        <v>-2.925</v>
+        <v>-2.415</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>0.93</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1232</v>
+        <v>-0.1046</v>
       </c>
       <c r="J111" t="n">
-        <v>-3.696</v>
+        <v>-3.138</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.39</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7252</v>
+        <v>0.6686</v>
       </c>
       <c r="J112" t="n">
-        <v>21.756</v>
+        <v>20.058</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>1.15</v>
       </c>
       <c r="I113" t="n">
-        <v>0.3392</v>
+        <v>0.2864</v>
       </c>
       <c r="J113" t="n">
-        <v>10.176</v>
+        <v>8.592000000000001</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>0.92</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1266</v>
+        <v>-0.1077</v>
       </c>
       <c r="J114" t="n">
-        <v>-3.798</v>
+        <v>-3.231</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>0.88</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1725</v>
+        <v>-0.152</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.175</v>
+        <v>-4.56</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.84</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2151</v>
+        <v>-0.1945</v>
       </c>
       <c r="J116" t="n">
-        <v>-6.453</v>
+        <v>-5.835</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.45</v>
       </c>
       <c r="I117" t="n">
-        <v>0.8099</v>
+        <v>0.7569</v>
       </c>
       <c r="J117" t="n">
-        <v>24.297</v>
+        <v>22.707</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.14</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3192</v>
+        <v>0.268</v>
       </c>
       <c r="J118" t="n">
-        <v>9.576000000000001</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>0.99</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0284</v>
+        <v>-0.0202</v>
       </c>
       <c r="J119" t="n">
-        <v>-0.852</v>
+        <v>-0.606</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>0.95</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.08989999999999999</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="J120" t="n">
-        <v>-2.697</v>
+        <v>-2.202</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.71</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3426</v>
+        <v>-0.3278</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.278</v>
+        <v>-9.834</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.32</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6243</v>
+        <v>0.5654</v>
       </c>
       <c r="J122" t="n">
-        <v>18.729</v>
+        <v>16.962</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.19</v>
       </c>
       <c r="I123" t="n">
-        <v>0.413</v>
+        <v>0.3562</v>
       </c>
       <c r="J123" t="n">
-        <v>12.39</v>
+        <v>10.686</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>1.13</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3066</v>
+        <v>0.2557</v>
       </c>
       <c r="J124" t="n">
-        <v>9.198</v>
+        <v>7.671</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>0.75</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3024</v>
+        <v>-0.2847</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.071999999999999</v>
+        <v>-8.541</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3582</v>
+        <v>-0.3444</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.746</v>
+        <v>-10.332</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.4</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7506</v>
+        <v>0.6964</v>
       </c>
       <c r="J127" t="n">
-        <v>22.518</v>
+        <v>20.892</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.03</v>
       </c>
       <c r="I128" t="n">
-        <v>0.0997</v>
+        <v>0.0737</v>
       </c>
       <c r="J128" t="n">
-        <v>2.991</v>
+        <v>2.211</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>0.98</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0428</v>
+        <v>-0.0325</v>
       </c>
       <c r="J129" t="n">
-        <v>-1.284</v>
+        <v>-0.975</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2426</v>
+        <v>-0.2225</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.278</v>
+        <v>-6.675</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.79</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2625</v>
+        <v>-0.2429</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.875</v>
+        <v>-7.287</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.43</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0304</v>
+        <v>1.0336</v>
       </c>
       <c r="J132" t="n">
-        <v>30.912</v>
+        <v>31.008</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.22</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6086</v>
+        <v>0.571</v>
       </c>
       <c r="J133" t="n">
-        <v>18.258</v>
+        <v>17.13</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>0.98</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1142</v>
+        <v>-0.0877</v>
       </c>
       <c r="J134" t="n">
-        <v>-3.426</v>
+        <v>-2.631</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>0.95</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2163</v>
+        <v>-0.1795</v>
       </c>
       <c r="J135" t="n">
-        <v>-6.489</v>
+        <v>-5.385</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.85</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4863</v>
+        <v>-0.4443</v>
       </c>
       <c r="J136" t="n">
-        <v>-14.589</v>
+        <v>-13.329</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.36</v>
       </c>
       <c r="I137" t="n">
-        <v>0.699</v>
+        <v>0.6438</v>
       </c>
       <c r="J137" t="n">
-        <v>20.97</v>
+        <v>19.314</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>1.2</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4401</v>
+        <v>0.3826</v>
       </c>
       <c r="J138" t="n">
-        <v>13.203</v>
+        <v>11.478</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>0.92</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1215</v>
+        <v>-0.1034</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.645</v>
+        <v>-3.102</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.76</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.289</v>
+        <v>-0.2704</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.67</v>
+        <v>-8.112</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.63</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4086</v>
+        <v>-0.399</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.258</v>
+        <v>-11.97</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.13</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3133</v>
+        <v>0.2617</v>
       </c>
       <c r="J142" t="n">
-        <v>9.398999999999999</v>
+        <v>7.851</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.04</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1272</v>
+        <v>0.096</v>
       </c>
       <c r="J143" t="n">
-        <v>3.816</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>0.95</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0847</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.541</v>
+        <v>-2.085</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>0.9</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1454</v>
+        <v>-0.126</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.362</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>0.89</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1567</v>
+        <v>-0.1368</v>
       </c>
       <c r="J146" t="n">
-        <v>-4.701</v>
+        <v>-4.104</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>1.54</v>
       </c>
       <c r="I147" t="n">
-        <v>0.9363</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="J147" t="n">
-        <v>28.089</v>
+        <v>26.778</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>1</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.0031</v>
+        <v>-0.0019</v>
       </c>
       <c r="J148" t="n">
-        <v>-0.093</v>
+        <v>-0.057</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>0.96</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.0765</v>
+        <v>-0.0613</v>
       </c>
       <c r="J149" t="n">
-        <v>-2.295</v>
+        <v>-1.839</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>0.93</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1158</v>
+        <v>-0.0974</v>
       </c>
       <c r="J150" t="n">
-        <v>-3.474</v>
+        <v>-2.922</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.83</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2268</v>
+        <v>-0.2065</v>
       </c>
       <c r="J151" t="n">
-        <v>-6.804</v>
+        <v>-6.195</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.51</v>
       </c>
       <c r="I152" t="n">
-        <v>1.1558</v>
+        <v>1.1726</v>
       </c>
       <c r="J152" t="n">
-        <v>32.3624</v>
+        <v>32.8328</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>1.06</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2212</v>
+        <v>0.1878</v>
       </c>
       <c r="J153" t="n">
-        <v>6.1936</v>
+        <v>5.2584</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>0.99</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0679</v>
+        <v>-0.0489</v>
       </c>
       <c r="J154" t="n">
-        <v>-1.9012</v>
+        <v>-1.3692</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.88</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4057</v>
+        <v>-0.3626</v>
       </c>
       <c r="J155" t="n">
-        <v>-11.3596</v>
+        <v>-10.1528</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.85</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4808</v>
+        <v>-0.4384</v>
       </c>
       <c r="J156" t="n">
-        <v>-13.4624</v>
+        <v>-12.2752</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.4</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7395</v>
+        <v>0.6834</v>
       </c>
       <c r="J157" t="n">
-        <v>20.706</v>
+        <v>19.1352</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.11</v>
       </c>
       <c r="I158" t="n">
-        <v>0.2654</v>
+        <v>0.2184</v>
       </c>
       <c r="J158" t="n">
-        <v>7.4312</v>
+        <v>6.1152</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>1.02</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0702</v>
+        <v>0.0511</v>
       </c>
       <c r="J159" t="n">
-        <v>1.9656</v>
+        <v>1.4308</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1021</v>
+        <v>-0.0847</v>
       </c>
       <c r="J160" t="n">
-        <v>-2.8588</v>
+        <v>-2.3716</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.72</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3325</v>
+        <v>-0.3169</v>
       </c>
       <c r="J161" t="n">
-        <v>-9.31</v>
+        <v>-8.873200000000001</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.24</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5087</v>
+        <v>0.4502</v>
       </c>
       <c r="J162" t="n">
-        <v>14.2436</v>
+        <v>12.6056</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>1</v>
       </c>
       <c r="I163" t="n">
-        <v>0.003</v>
+        <v>0.0015</v>
       </c>
       <c r="J163" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>1</v>
       </c>
       <c r="I164" t="n">
-        <v>0.003</v>
+        <v>0.0015</v>
       </c>
       <c r="J164" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>0.82</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2296</v>
+        <v>-0.2093</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.4288</v>
+        <v>-5.8604</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>0.79</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2595</v>
+        <v>-0.2398</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.266</v>
+        <v>-6.7144</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.47</v>
       </c>
       <c r="I167" t="n">
-        <v>1.0865</v>
+        <v>1.0977</v>
       </c>
       <c r="J167" t="n">
-        <v>30.422</v>
+        <v>30.7356</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>1.33</v>
       </c>
       <c r="I168" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.8146</v>
       </c>
       <c r="J168" t="n">
-        <v>23.4696</v>
+        <v>22.8088</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>1.08</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2723</v>
+        <v>0.2376</v>
       </c>
       <c r="J169" t="n">
-        <v>7.6244</v>
+        <v>6.6528</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>0.9</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3617</v>
+        <v>-0.3192</v>
       </c>
       <c r="J170" t="n">
-        <v>-10.1276</v>
+        <v>-8.9376</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.72</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7855</v>
+        <v>-0.761</v>
       </c>
       <c r="J171" t="n">
-        <v>-21.994</v>
+        <v>-21.308</v>
       </c>
     </row>
     <row r="172">
@@ -8769,10 +8769,10 @@
         <v>0.64</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.3337</v>
+        <v>-0.3244</v>
       </c>
       <c r="J172" t="n">
-        <v>-6.674</v>
+        <v>-6.488</v>
       </c>
     </row>
     <row r="173">
@@ -8809,10 +8809,10 @@
         <v>0.59</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.3832</v>
+        <v>-0.3783</v>
       </c>
       <c r="J173" t="n">
-        <v>-7.664</v>
+        <v>-7.566</v>
       </c>
     </row>
     <row r="174">
@@ -8849,10 +8849,10 @@
         <v>0.55</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.421</v>
+        <v>-0.4186</v>
       </c>
       <c r="J174" t="n">
-        <v>-8.42</v>
+        <v>-8.372</v>
       </c>
     </row>
     <row r="175">
@@ -8889,10 +8889,10 @@
         <v>0.39</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.5595</v>
+        <v>-0.5647</v>
       </c>
       <c r="J175" t="n">
-        <v>-11.19</v>
+        <v>-11.294</v>
       </c>
     </row>
     <row r="176">
@@ -8929,10 +8929,10 @@
         <v>0.29</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6504</v>
+        <v>-0.6688</v>
       </c>
       <c r="J176" t="n">
-        <v>-13.008</v>
+        <v>-13.376</v>
       </c>
     </row>
     <row r="177">
@@ -8969,10 +8969,10 @@
         <v>2.16</v>
       </c>
       <c r="I177" t="n">
-        <v>1.8236</v>
+        <v>1.8827</v>
       </c>
       <c r="J177" t="n">
-        <v>36.472</v>
+        <v>37.654</v>
       </c>
     </row>
     <row r="178">
@@ -9009,10 +9009,10 @@
         <v>1.69</v>
       </c>
       <c r="I178" t="n">
-        <v>1.2849</v>
+        <v>1.31</v>
       </c>
       <c r="J178" t="n">
-        <v>25.698</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="179">
@@ -9049,10 +9049,10 @@
         <v>1.58</v>
       </c>
       <c r="I179" t="n">
-        <v>1.1537</v>
+        <v>1.1764</v>
       </c>
       <c r="J179" t="n">
-        <v>23.074</v>
+        <v>23.528</v>
       </c>
     </row>
     <row r="180">
@@ -9089,10 +9089,10 @@
         <v>1.57</v>
       </c>
       <c r="I180" t="n">
-        <v>1.1413</v>
+        <v>1.1639</v>
       </c>
       <c r="J180" t="n">
-        <v>22.826</v>
+        <v>23.278</v>
       </c>
     </row>
     <row r="181">
@@ -9129,10 +9129,10 @@
         <v>1.19</v>
       </c>
       <c r="I181" t="n">
-        <v>0.4622</v>
+        <v>0.4303</v>
       </c>
       <c r="J181" t="n">
-        <v>9.244</v>
+        <v>8.606</v>
       </c>
     </row>
   </sheetData>
